--- a/cache/open_items_2026-06-15.xlsx
+++ b/cache/open_items_2026-06-15.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N294"/>
+  <dimension ref="A1:N295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
+          <t>SIGNAL-ALERTS-1</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
@@ -12186,22 +12186,22 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Daily WATCH-to-BUY flip + new Elite Pick alerts</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>Owner wanted Slack alerts for (a) firm BUY-candidate from entry-watcher, (b) names flipping to BUY day-over-day, (c) new Elite Picks per mode</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>entry_watch.py: distinct shadow BUY-CANDIDATE message (#a). signal_alerts.py: day-over-day diff of per-mode BUY lists (buy_candidates/medium_term_picks/long_term_picks) + elite_picks vs data/signal_alert_snapshot.json; grouped digest; LIVE to owner Slack with composite-score caveat; launchd com.swingtrade.signal-alerts 7:15 PT daily. Zero EODHD</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
@@ -12214,23 +12214,23 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>116e27f63</t>
         </is>
       </c>
       <c r="N210" s="8" t="inlineStr"/>
     </row>
-    <row r="211" ht="75" customHeight="1">
+    <row r="211" ht="90" customHeight="1">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>WEEKEND-PHANTOMS</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -12240,22 +12240,22 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
@@ -12273,18 +12273,18 @@
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N211" s="8" t="inlineStr"/>
     </row>
-    <row r="212" ht="60" customHeight="1">
+    <row r="212" ht="75" customHeight="1">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12294,22 +12294,22 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
@@ -12322,23 +12322,23 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N212" s="8" t="inlineStr"/>
     </row>
-    <row r="213" ht="45" customHeight="1">
+    <row r="213" ht="60" customHeight="1">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12348,22 +12348,22 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr"/>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12402,22 +12402,22 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr"/>
@@ -12430,12 +12430,12 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N214" s="8" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12785,17 +12785,17 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12813,7 +12813,7 @@
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N221" s="8" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13428,22 +13428,22 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13456,23 +13456,23 @@
       </c>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N233" s="8" t="inlineStr"/>
     </row>
-    <row r="234" ht="105" customHeight="1">
+    <row r="234" ht="45" customHeight="1">
       <c r="A234" s="2" t="n">
         <v>233</v>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13482,22 +13482,22 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13515,18 +13515,18 @@
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N234" s="8" t="inlineStr"/>
     </row>
-    <row r="235" ht="75" customHeight="1">
+    <row r="235" ht="105" customHeight="1">
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-T1CAT-1</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13536,22 +13536,22 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>T1 CATALYST pill read wrong field</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13564,12 +13564,12 @@
       </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N235" s="8" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>SCANNER-T1CAT-1</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13590,22 +13590,22 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>T1 CATALYST pill read wrong field</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13618,12 +13618,12 @@
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N236" s="8" t="inlineStr"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13672,23 +13672,23 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>613f10e35</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N237" s="8" t="inlineStr"/>
     </row>
-    <row r="238" ht="60" customHeight="1">
+    <row r="238" ht="75" customHeight="1">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13698,22 +13698,22 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13726,12 +13726,12 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>613f10e35</t>
         </is>
       </c>
       <c r="N238" s="8" t="inlineStr"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13752,34 +13752,26 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H239" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr"/>
+      <c r="I239" s="5" t="inlineStr"/>
       <c r="J239" s="5" t="inlineStr"/>
       <c r="K239" s="12" t="inlineStr">
         <is>
@@ -13788,27 +13780,23 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N239" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N239" s="8" t="inlineStr"/>
+    </row>
+    <row r="240" ht="60" customHeight="1">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -13823,17 +13811,17 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -13843,14 +13831,10 @@
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J240" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J240" s="5" t="inlineStr"/>
       <c r="K240" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13863,12 +13847,12 @@
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N240" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13862,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -13893,22 +13877,34 @@
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H241" s="2" t="inlineStr"/>
-      <c r="I241" s="5" t="inlineStr"/>
-      <c r="J241" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I241" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J241" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K241" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13916,23 +13912,27 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N241" s="8" t="inlineStr"/>
-    </row>
-    <row r="242" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N241" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="75" customHeight="1">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -13942,22 +13942,22 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr"/>
@@ -13970,23 +13970,23 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N242" s="8" t="inlineStr"/>
     </row>
-    <row r="243" ht="45" customHeight="1">
+    <row r="243" ht="60" customHeight="1">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -13996,34 +13996,26 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr"/>
+      <c r="I243" s="5" t="inlineStr"/>
       <c r="J243" s="5" t="inlineStr"/>
       <c r="K243" s="12" t="inlineStr">
         <is>
@@ -14032,27 +14024,23 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N243" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="90" customHeight="1">
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N243" s="8" t="inlineStr"/>
+    </row>
+    <row r="244" ht="45" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14062,26 +14050,34 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr"/>
-      <c r="I244" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I244" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J244" s="5" t="inlineStr"/>
       <c r="K244" s="12" t="inlineStr">
         <is>
@@ -14090,23 +14086,27 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N244" s="8" t="inlineStr"/>
-    </row>
-    <row r="245" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N244" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="90" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14116,39 +14116,27 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H245" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J245" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr"/>
+      <c r="I245" s="5" t="inlineStr"/>
+      <c r="J245" s="5" t="inlineStr"/>
       <c r="K245" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14156,19 +14144,15 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N245" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N245" s="8" t="inlineStr"/>
     </row>
     <row r="246" ht="45" customHeight="1">
       <c r="A246" s="2" t="n">
@@ -14176,7 +14160,7 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14186,27 +14170,39 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr"/>
-      <c r="I246" s="5" t="inlineStr"/>
-      <c r="J246" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I246" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J246" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K246" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14214,15 +14210,19 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N246" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N246" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="45" customHeight="1">
       <c r="A247" s="2" t="n">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14240,22 +14240,22 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr"/>
@@ -14273,18 +14273,18 @@
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N247" s="8" t="inlineStr"/>
     </row>
-    <row r="248" ht="75" customHeight="1">
+    <row r="248" ht="45" customHeight="1">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14294,39 +14294,27 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I248" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J248" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="5" t="inlineStr"/>
+      <c r="J248" s="5" t="inlineStr"/>
       <c r="K248" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14334,27 +14322,23 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N248" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N248" s="8" t="inlineStr"/>
+    </row>
+    <row r="249" ht="75" customHeight="1">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14364,37 +14348,37 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J249" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K249" s="12" t="inlineStr">
@@ -14404,17 +14388,17 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N249" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14408,7 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14439,32 +14423,32 @@
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J250" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K250" s="12" t="inlineStr">
@@ -14484,7 +14468,7 @@
       </c>
       <c r="N250" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -14494,7 +14478,7 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14509,32 +14493,32 @@
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K251" s="12" t="inlineStr">
@@ -14554,7 +14538,7 @@
       </c>
       <c r="N251" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14548,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14579,32 +14563,32 @@
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K252" s="12" t="inlineStr">
@@ -14614,27 +14598,27 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N252" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="60" customHeight="1">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14644,27 +14628,39 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H253" s="2" t="inlineStr"/>
-      <c r="I253" s="5" t="inlineStr"/>
-      <c r="J253" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I253" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J253" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K253" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14672,15 +14668,19 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N253" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N253" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="45" customHeight="1">
       <c r="A254" s="2" t="n">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14698,22 +14698,22 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr"/>
@@ -14736,13 +14736,13 @@
       </c>
       <c r="N254" s="8" t="inlineStr"/>
     </row>
-    <row r="255" ht="60" customHeight="1">
+    <row r="255" ht="45" customHeight="1">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14752,22 +14752,22 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr"/>
@@ -14780,23 +14780,23 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N255" s="8" t="inlineStr"/>
     </row>
-    <row r="256" ht="150" customHeight="1">
+    <row r="256" ht="60" customHeight="1">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
@@ -14806,31 +14806,27 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
       <c r="I256" s="5" t="inlineStr"/>
-      <c r="J256" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J256" s="5" t="inlineStr"/>
       <c r="K256" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14838,27 +14834,23 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N256" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="105" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N256" s="8" t="inlineStr"/>
+    </row>
+    <row r="257" ht="150" customHeight="1">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
@@ -14868,27 +14860,31 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
       <c r="I257" s="5" t="inlineStr"/>
-      <c r="J257" s="5" t="inlineStr"/>
+      <c r="J257" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K257" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14896,23 +14892,27 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
-        </is>
-      </c>
-      <c r="N257" s="8" t="inlineStr"/>
-    </row>
-    <row r="258" ht="45" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N257" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="105" customHeight="1">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
@@ -14922,22 +14922,22 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
@@ -14950,12 +14950,12 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N258" s="8" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -14981,17 +14981,17 @@
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -15035,17 +15035,17 @@
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -15089,17 +15089,17 @@
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
@@ -15143,17 +15143,17 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
@@ -15197,17 +15197,17 @@
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15251,17 +15251,17 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15305,17 +15305,17 @@
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15467,17 +15467,17 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15521,17 +15521,17 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -15554,13 +15554,13 @@
       </c>
       <c r="N269" s="8" t="inlineStr"/>
     </row>
-    <row r="270" ht="60" customHeight="1">
+    <row r="270" ht="45" customHeight="1">
       <c r="A270" s="2" t="n">
         <v>269</v>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15570,22 +15570,22 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -15598,23 +15598,23 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N270" s="8" t="inlineStr"/>
     </row>
-    <row r="271" ht="120" customHeight="1">
+    <row r="271" ht="60" customHeight="1">
       <c r="A271" s="2" t="n">
         <v>270</v>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15624,39 +15624,27 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H271" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I271" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J271" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr"/>
+      <c r="I271" s="5" t="inlineStr"/>
+      <c r="J271" s="5" t="inlineStr"/>
       <c r="K271" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15664,27 +15652,23 @@
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N271" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="75" customHeight="1">
+          <t>cf702f2b4</t>
+        </is>
+      </c>
+      <c r="N271" s="8" t="inlineStr"/>
+    </row>
+    <row r="272" ht="120" customHeight="1">
       <c r="A272" s="2" t="n">
         <v>271</v>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15694,27 +15678,39 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H272" s="2" t="inlineStr"/>
-      <c r="I272" s="5" t="inlineStr"/>
-      <c r="J272" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I272" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J272" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K272" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15722,23 +15718,27 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N272" s="8" t="inlineStr"/>
-    </row>
-    <row r="273" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N272" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="75" customHeight="1">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15748,22 +15748,22 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
@@ -15776,23 +15776,23 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N273" s="8" t="inlineStr"/>
     </row>
-    <row r="274" ht="45" customHeight="1">
+    <row r="274" ht="60" customHeight="1">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -15840,13 +15840,13 @@
       </c>
       <c r="N274" s="8" t="inlineStr"/>
     </row>
-    <row r="275" ht="60" customHeight="1">
+    <row r="275" ht="45" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15861,17 +15861,17 @@
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -15894,13 +15894,13 @@
       </c>
       <c r="N275" s="8" t="inlineStr"/>
     </row>
-    <row r="276" ht="45" customHeight="1">
+    <row r="276" ht="60" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15915,17 +15915,17 @@
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N276" s="8" t="inlineStr"/>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15969,17 +15969,17 @@
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
@@ -16002,13 +16002,13 @@
       </c>
       <c r="N277" s="8" t="inlineStr"/>
     </row>
-    <row r="278" ht="120" customHeight="1">
+    <row r="278" ht="45" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -16018,22 +16018,22 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -16046,23 +16046,23 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N278" s="8" t="inlineStr"/>
     </row>
-    <row r="279" ht="60" customHeight="1">
+    <row r="279" ht="120" customHeight="1">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -16072,22 +16072,22 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -16100,23 +16100,23 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>93ec11842</t>
         </is>
       </c>
       <c r="N279" s="8" t="inlineStr"/>
     </row>
-    <row r="280" ht="105" customHeight="1">
+    <row r="280" ht="60" customHeight="1">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16126,31 +16126,27 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
       <c r="I280" s="5" t="inlineStr"/>
-      <c r="J280" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J280" s="5" t="inlineStr"/>
       <c r="K280" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16158,27 +16154,23 @@
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N280" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="135" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N280" s="8" t="inlineStr"/>
+    </row>
+    <row r="281" ht="105" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16188,37 +16180,29 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H281" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I281" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr"/>
+      <c r="I281" s="5" t="inlineStr"/>
       <c r="J281" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K281" s="12" t="inlineStr">
@@ -16228,27 +16212,27 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N281" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="135" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16258,27 +16242,39 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H282" s="2" t="inlineStr"/>
-      <c r="I282" s="5" t="inlineStr"/>
-      <c r="J282" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I282" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J282" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K282" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16286,23 +16282,27 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N282" s="8" t="inlineStr"/>
-    </row>
-    <row r="283" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N282" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="45" customHeight="1">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16312,31 +16312,27 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr"/>
       <c r="I283" s="5" t="inlineStr"/>
-      <c r="J283" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J283" s="5" t="inlineStr"/>
       <c r="K283" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16344,27 +16340,23 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N283" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N283" s="8" t="inlineStr"/>
+    </row>
+    <row r="284" ht="120" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16374,27 +16366,31 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
       <c r="I284" s="5" t="inlineStr"/>
-      <c r="J284" s="5" t="inlineStr"/>
+      <c r="J284" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K284" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16402,15 +16398,19 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N284" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N284" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="60" customHeight="1">
       <c r="A285" s="2" t="n">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16428,22 +16428,22 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr"/>
@@ -16461,60 +16461,48 @@
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N285" s="8" t="inlineStr"/>
     </row>
-    <row r="286" ht="45" customHeight="1">
+    <row r="286" ht="60" customHeight="1">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C286" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C286" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H286" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I286" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J286" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="5" t="inlineStr"/>
+      <c r="J286" s="5" t="inlineStr"/>
       <c r="K286" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16522,15 +16510,15 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M286" s="3" t="inlineStr"/>
-      <c r="N286" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N286" s="8" t="inlineStr"/>
     </row>
     <row r="287" ht="45" customHeight="1">
       <c r="A287" s="2" t="n">
@@ -16538,7 +16526,7 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C287" s="13" t="inlineStr">
@@ -16553,32 +16541,32 @@
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J287" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K287" s="12" t="inlineStr">
@@ -16594,7 +16582,7 @@
       <c r="M287" s="3" t="inlineStr"/>
       <c r="N287" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -16604,7 +16592,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
@@ -16614,35 +16602,39 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J288" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J288" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K288" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16650,17 +16642,13 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M288" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr"/>
       <c r="N288" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -16670,59 +16658,63 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C289" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C289" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J289" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K289" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L289" s="2" t="inlineStr"/>
-      <c r="M289" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J289" s="5" t="inlineStr"/>
+      <c r="K289" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N289" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -16732,7 +16724,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C290" s="10" t="inlineStr">
@@ -16742,37 +16734,37 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J290" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K290" s="14" t="inlineStr">
@@ -16794,109 +16786,109 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C291" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C291" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K291" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K291" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L291" s="2" t="inlineStr"/>
       <c r="M291" s="3" t="inlineStr"/>
       <c r="N291" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="45" customHeight="1">
       <c r="A292" s="2" t="n">
         <v>291</v>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C292" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J292" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K292" s="15" t="inlineStr">
@@ -16904,147 +16896,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L292" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L292" s="2" t="inlineStr"/>
       <c r="M292" s="3" t="inlineStr"/>
       <c r="N292" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="75" customHeight="1">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E293" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I293" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J293" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K293" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr"/>
+      <c r="N293" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="195" customHeight="1">
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C293" s="10" t="inlineStr">
+      <c r="C294" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E294" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G293" s="5" t="inlineStr">
+      <c r="G294" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H293" s="2" t="inlineStr">
+      <c r="H294" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J293" s="5" t="inlineStr">
+      <c r="J294" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K293" s="15" t="inlineStr">
+      <c r="K294" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L293" s="2" t="inlineStr">
+      <c r="L294" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M293" s="3" t="inlineStr"/>
-      <c r="N293" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="90" customHeight="1">
-      <c r="A294" s="2" t="n">
-        <v>293</v>
-      </c>
-      <c r="B294" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C294" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E294" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H294" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I294" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J294" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K294" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L294" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M294" s="3" t="inlineStr"/>
       <c r="N294" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="90" customHeight="1">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C295" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E295" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I295" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J295" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K295" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr"/>
+      <c r="N295" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -17149,10 +17203,10 @@
         <v>86</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
@@ -17206,10 +17260,10 @@
         <v>111</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-15.xlsx
+++ b/cache/open_items_2026-06-15.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N295"/>
+  <dimension ref="A1:N296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>SIGNAL-ALERTS-1</t>
+          <t>MORNING-BRIEF-STALE</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Daily WATCH-to-BUY flip + new Elite Pick alerts</t>
+          <t>Morning briefing exit=2 (stale tickers.json)</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Owner wanted Slack alerts for (a) firm BUY-candidate from entry-watcher, (b) names flipping to BUY day-over-day, (c) new Elite Picks per mode</t>
+          <t>morning_briefing.py aborts (exit 2) when infra/prototype/tickers.json &gt;24h old. Root cause: build_data.py (writes tickers.json at scan end) intermittently exceeds the 180s subprocess timeout in swing_trade.py on cold caches -&gt; tickers.json not refreshed -&gt; stale -&gt; briefing aborts. Compounded by transient Slack DNS failures when the Mac is asleep at 6:30am</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>entry_watch.py: distinct shadow BUY-CANDIDATE message (#a). signal_alerts.py: day-over-day diff of per-mode BUY lists (buy_candidates/medium_term_picks/long_term_picks) + elite_picks vs data/signal_alert_snapshot.json; grouped digest; LIVE to owner Slack with composite-score caveat; launchd com.swingtrade.signal-alerts 7:15 PT daily. Zero EODHD</t>
+          <t>Raised build_data.py subprocess timeout 180-&gt;360s in swing_trade.py (2x headroom). Manually refreshed tickers.json. Residual: machine must be awake/online at 6:30 PT for briefing+all alerts to post</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>116e27f63</t>
+          <t>e7721f05c</t>
         </is>
       </c>
       <c r="N210" s="8" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
+          <t>SIGNAL-ALERTS-1</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -12240,22 +12240,22 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Daily WATCH-to-BUY flip + new Elite Pick alerts</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>Owner wanted Slack alerts for (a) firm BUY-candidate from entry-watcher, (b) names flipping to BUY day-over-day, (c) new Elite Picks per mode</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>entry_watch.py: distinct shadow BUY-CANDIDATE message (#a). signal_alerts.py: day-over-day diff of per-mode BUY lists (buy_candidates/medium_term_picks/long_term_picks) + elite_picks vs data/signal_alert_snapshot.json; grouped digest; LIVE to owner Slack with composite-score caveat; launchd com.swingtrade.signal-alerts 7:15 PT daily. Zero EODHD</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
@@ -12268,23 +12268,23 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>116e27f63</t>
         </is>
       </c>
       <c r="N211" s="8" t="inlineStr"/>
     </row>
-    <row r="212" ht="75" customHeight="1">
+    <row r="212" ht="90" customHeight="1">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>WEEKEND-PHANTOMS</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12294,22 +12294,22 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
@@ -12327,18 +12327,18 @@
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N212" s="8" t="inlineStr"/>
     </row>
-    <row r="213" ht="60" customHeight="1">
+    <row r="213" ht="75" customHeight="1">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12348,22 +12348,22 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr"/>
@@ -12376,23 +12376,23 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N213" s="8" t="inlineStr"/>
     </row>
-    <row r="214" ht="45" customHeight="1">
+    <row r="214" ht="60" customHeight="1">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12402,22 +12402,22 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12456,22 +12456,22 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12484,12 +12484,12 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N215" s="8" t="inlineStr"/>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12839,17 +12839,17 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N222" s="8" t="inlineStr"/>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13482,22 +13482,22 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13510,23 +13510,23 @@
       </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N234" s="8" t="inlineStr"/>
     </row>
-    <row r="235" ht="105" customHeight="1">
+    <row r="235" ht="45" customHeight="1">
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13536,22 +13536,22 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13569,18 +13569,18 @@
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N235" s="8" t="inlineStr"/>
     </row>
-    <row r="236" ht="75" customHeight="1">
+    <row r="236" ht="105" customHeight="1">
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-T1CAT-1</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13590,22 +13590,22 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>T1 CATALYST pill read wrong field</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13618,12 +13618,12 @@
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N236" s="8" t="inlineStr"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>SCANNER-T1CAT-1</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>T1 CATALYST pill read wrong field</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N237" s="8" t="inlineStr"/>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13698,22 +13698,22 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13726,23 +13726,23 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>613f10e35</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N238" s="8" t="inlineStr"/>
     </row>
-    <row r="239" ht="60" customHeight="1">
+    <row r="239" ht="75" customHeight="1">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13752,22 +13752,22 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -13780,12 +13780,12 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>613f10e35</t>
         </is>
       </c>
       <c r="N239" s="8" t="inlineStr"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -13806,34 +13806,26 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H240" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I240" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr"/>
+      <c r="I240" s="5" t="inlineStr"/>
       <c r="J240" s="5" t="inlineStr"/>
       <c r="K240" s="12" t="inlineStr">
         <is>
@@ -13842,27 +13834,23 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N240" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N240" s="8" t="inlineStr"/>
+    </row>
+    <row r="241" ht="60" customHeight="1">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -13877,17 +13865,17 @@
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -13897,14 +13885,10 @@
       </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J241" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J241" s="5" t="inlineStr"/>
       <c r="K241" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13917,12 +13901,12 @@
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N241" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13916,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -13947,22 +13931,34 @@
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr"/>
-      <c r="I242" s="5" t="inlineStr"/>
-      <c r="J242" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K242" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13970,23 +13966,27 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N242" s="8" t="inlineStr"/>
-    </row>
-    <row r="243" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N242" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="75" customHeight="1">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -13996,22 +13996,22 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr"/>
@@ -14024,23 +14024,23 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N243" s="8" t="inlineStr"/>
     </row>
-    <row r="244" ht="45" customHeight="1">
+    <row r="244" ht="60" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14050,34 +14050,26 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I244" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="5" t="inlineStr"/>
       <c r="J244" s="5" t="inlineStr"/>
       <c r="K244" s="12" t="inlineStr">
         <is>
@@ -14086,27 +14078,23 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N244" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="90" customHeight="1">
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N244" s="8" t="inlineStr"/>
+    </row>
+    <row r="245" ht="45" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14116,26 +14104,34 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
-        </is>
-      </c>
-      <c r="H245" s="2" t="inlineStr"/>
-      <c r="I245" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I245" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J245" s="5" t="inlineStr"/>
       <c r="K245" s="12" t="inlineStr">
         <is>
@@ -14144,23 +14140,27 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N245" s="8" t="inlineStr"/>
-    </row>
-    <row r="246" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N245" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="90" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14170,39 +14170,27 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I246" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J246" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="5" t="inlineStr"/>
+      <c r="J246" s="5" t="inlineStr"/>
       <c r="K246" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14210,19 +14198,15 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N246" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N246" s="8" t="inlineStr"/>
     </row>
     <row r="247" ht="45" customHeight="1">
       <c r="A247" s="2" t="n">
@@ -14230,7 +14214,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14240,27 +14224,39 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="inlineStr"/>
-      <c r="I247" s="5" t="inlineStr"/>
-      <c r="J247" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I247" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J247" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K247" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14268,15 +14264,19 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N247" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N247" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="45" customHeight="1">
       <c r="A248" s="2" t="n">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14294,22 +14294,22 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr"/>
@@ -14327,18 +14327,18 @@
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N248" s="8" t="inlineStr"/>
     </row>
-    <row r="249" ht="75" customHeight="1">
+    <row r="249" ht="45" customHeight="1">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14348,39 +14348,27 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I249" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J249" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr"/>
+      <c r="I249" s="5" t="inlineStr"/>
+      <c r="J249" s="5" t="inlineStr"/>
       <c r="K249" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14388,27 +14376,23 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N249" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N249" s="8" t="inlineStr"/>
+    </row>
+    <row r="250" ht="75" customHeight="1">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14418,37 +14402,37 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J250" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K250" s="12" t="inlineStr">
@@ -14458,17 +14442,17 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N250" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14462,7 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14493,32 +14477,32 @@
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K251" s="12" t="inlineStr">
@@ -14538,7 +14522,7 @@
       </c>
       <c r="N251" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14532,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14563,32 +14547,32 @@
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K252" s="12" t="inlineStr">
@@ -14608,7 +14592,7 @@
       </c>
       <c r="N252" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14602,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14633,32 +14617,32 @@
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K253" s="12" t="inlineStr">
@@ -14668,27 +14652,27 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N253" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="60" customHeight="1">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14698,27 +14682,39 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H254" s="2" t="inlineStr"/>
-      <c r="I254" s="5" t="inlineStr"/>
-      <c r="J254" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I254" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J254" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K254" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14726,15 +14722,19 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N254" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N254" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="45" customHeight="1">
       <c r="A255" s="2" t="n">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14752,22 +14752,22 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr"/>
@@ -14790,13 +14790,13 @@
       </c>
       <c r="N255" s="8" t="inlineStr"/>
     </row>
-    <row r="256" ht="60" customHeight="1">
+    <row r="256" ht="45" customHeight="1">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
@@ -14806,22 +14806,22 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
@@ -14834,23 +14834,23 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N256" s="8" t="inlineStr"/>
     </row>
-    <row r="257" ht="150" customHeight="1">
+    <row r="257" ht="60" customHeight="1">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
@@ -14860,31 +14860,27 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
       <c r="I257" s="5" t="inlineStr"/>
-      <c r="J257" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J257" s="5" t="inlineStr"/>
       <c r="K257" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14892,27 +14888,23 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N257" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="105" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N257" s="8" t="inlineStr"/>
+    </row>
+    <row r="258" ht="150" customHeight="1">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
@@ -14922,27 +14914,31 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
       <c r="I258" s="5" t="inlineStr"/>
-      <c r="J258" s="5" t="inlineStr"/>
+      <c r="J258" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K258" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14950,23 +14946,27 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
-        </is>
-      </c>
-      <c r="N258" s="8" t="inlineStr"/>
-    </row>
-    <row r="259" ht="45" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N258" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="105" customHeight="1">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -14976,22 +14976,22 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
@@ -15004,12 +15004,12 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N259" s="8" t="inlineStr"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -15035,17 +15035,17 @@
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -15089,17 +15089,17 @@
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
@@ -15143,17 +15143,17 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
@@ -15197,17 +15197,17 @@
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15251,17 +15251,17 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15305,17 +15305,17 @@
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15467,17 +15467,17 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15521,17 +15521,17 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15575,17 +15575,17 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -15608,13 +15608,13 @@
       </c>
       <c r="N270" s="8" t="inlineStr"/>
     </row>
-    <row r="271" ht="60" customHeight="1">
+    <row r="271" ht="45" customHeight="1">
       <c r="A271" s="2" t="n">
         <v>270</v>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15624,22 +15624,22 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -15652,23 +15652,23 @@
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N271" s="8" t="inlineStr"/>
     </row>
-    <row r="272" ht="120" customHeight="1">
+    <row r="272" ht="60" customHeight="1">
       <c r="A272" s="2" t="n">
         <v>271</v>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15678,39 +15678,27 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H272" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I272" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J272" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr"/>
+      <c r="I272" s="5" t="inlineStr"/>
+      <c r="J272" s="5" t="inlineStr"/>
       <c r="K272" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15718,27 +15706,23 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N272" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="75" customHeight="1">
+          <t>cf702f2b4</t>
+        </is>
+      </c>
+      <c r="N272" s="8" t="inlineStr"/>
+    </row>
+    <row r="273" ht="120" customHeight="1">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15748,27 +15732,39 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H273" s="2" t="inlineStr"/>
-      <c r="I273" s="5" t="inlineStr"/>
-      <c r="J273" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I273" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J273" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K273" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15776,23 +15772,27 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N273" s="8" t="inlineStr"/>
-    </row>
-    <row r="274" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N273" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="75" customHeight="1">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15802,22 +15802,22 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -15830,23 +15830,23 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N274" s="8" t="inlineStr"/>
     </row>
-    <row r="275" ht="45" customHeight="1">
+    <row r="275" ht="60" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15861,17 +15861,17 @@
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -15894,13 +15894,13 @@
       </c>
       <c r="N275" s="8" t="inlineStr"/>
     </row>
-    <row r="276" ht="60" customHeight="1">
+    <row r="276" ht="45" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15915,17 +15915,17 @@
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -15948,13 +15948,13 @@
       </c>
       <c r="N276" s="8" t="inlineStr"/>
     </row>
-    <row r="277" ht="45" customHeight="1">
+    <row r="277" ht="60" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15969,17 +15969,17 @@
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
@@ -15997,7 +15997,7 @@
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N277" s="8" t="inlineStr"/>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -16023,17 +16023,17 @@
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -16056,13 +16056,13 @@
       </c>
       <c r="N278" s="8" t="inlineStr"/>
     </row>
-    <row r="279" ht="120" customHeight="1">
+    <row r="279" ht="45" customHeight="1">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -16072,22 +16072,22 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -16100,23 +16100,23 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N279" s="8" t="inlineStr"/>
     </row>
-    <row r="280" ht="60" customHeight="1">
+    <row r="280" ht="120" customHeight="1">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16126,22 +16126,22 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -16154,23 +16154,23 @@
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>93ec11842</t>
         </is>
       </c>
       <c r="N280" s="8" t="inlineStr"/>
     </row>
-    <row r="281" ht="105" customHeight="1">
+    <row r="281" ht="60" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16180,31 +16180,27 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
       <c r="I281" s="5" t="inlineStr"/>
-      <c r="J281" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J281" s="5" t="inlineStr"/>
       <c r="K281" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16212,27 +16208,23 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N281" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="135" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N281" s="8" t="inlineStr"/>
+    </row>
+    <row r="282" ht="105" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16242,37 +16234,29 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H282" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I282" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr"/>
+      <c r="I282" s="5" t="inlineStr"/>
       <c r="J282" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K282" s="12" t="inlineStr">
@@ -16282,27 +16266,27 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N282" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="135" customHeight="1">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16312,27 +16296,39 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H283" s="2" t="inlineStr"/>
-      <c r="I283" s="5" t="inlineStr"/>
-      <c r="J283" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I283" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J283" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K283" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16340,23 +16336,27 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N283" s="8" t="inlineStr"/>
-    </row>
-    <row r="284" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N283" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="45" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16366,31 +16366,27 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
       <c r="I284" s="5" t="inlineStr"/>
-      <c r="J284" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J284" s="5" t="inlineStr"/>
       <c r="K284" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16398,27 +16394,23 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N284" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N284" s="8" t="inlineStr"/>
+    </row>
+    <row r="285" ht="120" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16428,27 +16420,31 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr"/>
       <c r="I285" s="5" t="inlineStr"/>
-      <c r="J285" s="5" t="inlineStr"/>
+      <c r="J285" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K285" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16456,15 +16452,19 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N285" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N285" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="60" customHeight="1">
       <c r="A286" s="2" t="n">
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16482,22 +16482,22 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr"/>
@@ -16515,60 +16515,48 @@
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N286" s="8" t="inlineStr"/>
     </row>
-    <row r="287" ht="45" customHeight="1">
+    <row r="287" ht="60" customHeight="1">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C287" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C287" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H287" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I287" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J287" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr"/>
+      <c r="I287" s="5" t="inlineStr"/>
+      <c r="J287" s="5" t="inlineStr"/>
       <c r="K287" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16576,15 +16564,15 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M287" s="3" t="inlineStr"/>
-      <c r="N287" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N287" s="8" t="inlineStr"/>
     </row>
     <row r="288" ht="45" customHeight="1">
       <c r="A288" s="2" t="n">
@@ -16592,7 +16580,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
@@ -16607,32 +16595,32 @@
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K288" s="12" t="inlineStr">
@@ -16648,7 +16636,7 @@
       <c r="M288" s="3" t="inlineStr"/>
       <c r="N288" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16646,7 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
@@ -16668,35 +16656,39 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J289" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J289" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K289" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16704,17 +16696,13 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M289" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M289" s="3" t="inlineStr"/>
       <c r="N289" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -16724,59 +16712,63 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C290" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C290" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J290" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K290" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L290" s="2" t="inlineStr"/>
-      <c r="M290" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J290" s="5" t="inlineStr"/>
+      <c r="K290" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N290" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -16786,7 +16778,7 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C291" s="10" t="inlineStr">
@@ -16796,37 +16788,37 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K291" s="14" t="inlineStr">
@@ -16848,109 +16840,109 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C292" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C292" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J292" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K292" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K292" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L292" s="2" t="inlineStr"/>
       <c r="M292" s="3" t="inlineStr"/>
       <c r="N292" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="45" customHeight="1">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C293" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K293" s="15" t="inlineStr">
@@ -16958,147 +16950,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L293" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L293" s="2" t="inlineStr"/>
       <c r="M293" s="3" t="inlineStr"/>
       <c r="N293" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="75" customHeight="1">
       <c r="A294" s="2" t="n">
         <v>293</v>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C294" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E294" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I294" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J294" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K294" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M294" s="3" t="inlineStr"/>
+      <c r="N294" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="195" customHeight="1">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C294" s="10" t="inlineStr">
+      <c r="C295" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E295" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G294" s="5" t="inlineStr">
+      <c r="G295" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H294" s="2" t="inlineStr">
+      <c r="H295" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J294" s="5" t="inlineStr">
+      <c r="J295" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K294" s="15" t="inlineStr">
+      <c r="K295" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L294" s="2" t="inlineStr">
+      <c r="L295" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M294" s="3" t="inlineStr"/>
-      <c r="N294" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="90" customHeight="1">
-      <c r="A295" s="2" t="n">
-        <v>294</v>
-      </c>
-      <c r="B295" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C295" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E295" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H295" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I295" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J295" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K295" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L295" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M295" s="3" t="inlineStr"/>
       <c r="N295" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="90" customHeight="1">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C296" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E296" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I296" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J296" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K296" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr"/>
+      <c r="N296" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -17203,10 +17257,10 @@
         <v>86</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
@@ -17260,10 +17314,10 @@
         <v>111</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-15.xlsx
+++ b/cache/open_items_2026-06-15.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N296"/>
+  <dimension ref="A1:N297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12278,13 +12278,13 @@
       </c>
       <c r="N211" s="8" t="inlineStr"/>
     </row>
-    <row r="212" ht="90" customHeight="1">
+    <row r="212" ht="75" customHeight="1">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
+          <t>SLEEVE-ALERTS</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12294,22 +12294,22 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Dedicated catalyst-sleeve signal alerts</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>Entry-watcher covers price-action setups (pullback/breakout/impulse) but the 7 catalyst sleeves (PEAD/Insider/ESP/MeanRev/Momentum/DefRot) had no dedicated alert — they only reached Slack indirectly via flip/elite digests. Per principle 14 these are the higher-mechanism signals (PEAD PF 2.04, Momentum 1.53)</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>signal_alerts.py: added SLEEVES dimension; _current_state tracks &lt;field&gt;.fired per sleeve; daily diff emits '🧬 New catalyst signal(s)' clean card on new entrants; Phase-1 paper-validation note. Fire rarely (0 today) so low-noise/high-value. Snapshot re-seeded with sleeves key</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
@@ -12322,23 +12322,23 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>fa8835903</t>
         </is>
       </c>
       <c r="N212" s="8" t="inlineStr"/>
     </row>
-    <row r="213" ht="75" customHeight="1">
+    <row r="213" ht="90" customHeight="1">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>WEEKEND-PHANTOMS</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12348,22 +12348,22 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr"/>
@@ -12381,18 +12381,18 @@
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N213" s="8" t="inlineStr"/>
     </row>
-    <row r="214" ht="60" customHeight="1">
+    <row r="214" ht="75" customHeight="1">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12402,22 +12402,22 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr"/>
@@ -12430,23 +12430,23 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N214" s="8" t="inlineStr"/>
     </row>
-    <row r="215" ht="45" customHeight="1">
+    <row r="215" ht="60" customHeight="1">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12456,22 +12456,22 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12510,22 +12510,22 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12538,12 +12538,12 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N216" s="8" t="inlineStr"/>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -12893,17 +12893,17 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N223" s="8" t="inlineStr"/>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13536,22 +13536,22 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13564,23 +13564,23 @@
       </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N235" s="8" t="inlineStr"/>
     </row>
-    <row r="236" ht="105" customHeight="1">
+    <row r="236" ht="45" customHeight="1">
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13590,22 +13590,22 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13623,18 +13623,18 @@
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N236" s="8" t="inlineStr"/>
     </row>
-    <row r="237" ht="75" customHeight="1">
+    <row r="237" ht="105" customHeight="1">
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-T1CAT-1</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>T1 CATALYST pill read wrong field</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N237" s="8" t="inlineStr"/>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>SCANNER-T1CAT-1</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13698,22 +13698,22 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>T1 CATALYST pill read wrong field</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13726,12 +13726,12 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N238" s="8" t="inlineStr"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13752,22 +13752,22 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -13780,23 +13780,23 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>613f10e35</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N239" s="8" t="inlineStr"/>
     </row>
-    <row r="240" ht="60" customHeight="1">
+    <row r="240" ht="75" customHeight="1">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -13806,22 +13806,22 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
@@ -13834,12 +13834,12 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>613f10e35</t>
         </is>
       </c>
       <c r="N240" s="8" t="inlineStr"/>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -13860,34 +13860,26 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H241" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I241" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr"/>
+      <c r="I241" s="5" t="inlineStr"/>
       <c r="J241" s="5" t="inlineStr"/>
       <c r="K241" s="12" t="inlineStr">
         <is>
@@ -13896,27 +13888,23 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N241" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N241" s="8" t="inlineStr"/>
+    </row>
+    <row r="242" ht="60" customHeight="1">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -13931,17 +13919,17 @@
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -13951,14 +13939,10 @@
       </c>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J242" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="inlineStr"/>
       <c r="K242" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13971,12 +13955,12 @@
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N242" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13970,7 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -14001,22 +13985,34 @@
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="inlineStr"/>
-      <c r="I243" s="5" t="inlineStr"/>
-      <c r="J243" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I243" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J243" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K243" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14024,23 +14020,27 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N243" s="8" t="inlineStr"/>
-    </row>
-    <row r="244" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N243" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="75" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr"/>
@@ -14078,23 +14078,23 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N244" s="8" t="inlineStr"/>
     </row>
-    <row r="245" ht="45" customHeight="1">
+    <row r="245" ht="60" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14104,34 +14104,26 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H245" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr"/>
+      <c r="I245" s="5" t="inlineStr"/>
       <c r="J245" s="5" t="inlineStr"/>
       <c r="K245" s="12" t="inlineStr">
         <is>
@@ -14140,27 +14132,23 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N245" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="90" customHeight="1">
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N245" s="8" t="inlineStr"/>
+    </row>
+    <row r="246" ht="45" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14170,26 +14158,34 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr"/>
-      <c r="I246" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I246" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J246" s="5" t="inlineStr"/>
       <c r="K246" s="12" t="inlineStr">
         <is>
@@ -14198,23 +14194,27 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N246" s="8" t="inlineStr"/>
-    </row>
-    <row r="247" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N246" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="90" customHeight="1">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14224,39 +14224,27 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I247" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J247" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr"/>
+      <c r="I247" s="5" t="inlineStr"/>
+      <c r="J247" s="5" t="inlineStr"/>
       <c r="K247" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14264,19 +14252,15 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N247" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N247" s="8" t="inlineStr"/>
     </row>
     <row r="248" ht="45" customHeight="1">
       <c r="A248" s="2" t="n">
@@ -14284,7 +14268,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14294,27 +14278,39 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H248" s="2" t="inlineStr"/>
-      <c r="I248" s="5" t="inlineStr"/>
-      <c r="J248" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I248" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J248" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K248" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14322,15 +14318,19 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N248" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N248" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="45" customHeight="1">
       <c r="A249" s="2" t="n">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14348,22 +14348,22 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr"/>
@@ -14381,18 +14381,18 @@
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N249" s="8" t="inlineStr"/>
     </row>
-    <row r="250" ht="75" customHeight="1">
+    <row r="250" ht="45" customHeight="1">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14402,39 +14402,27 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I250" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J250" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="5" t="inlineStr"/>
+      <c r="J250" s="5" t="inlineStr"/>
       <c r="K250" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14442,27 +14430,23 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N250" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N250" s="8" t="inlineStr"/>
+    </row>
+    <row r="251" ht="75" customHeight="1">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14472,37 +14456,37 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K251" s="12" t="inlineStr">
@@ -14512,17 +14496,17 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N251" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14516,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14547,32 +14531,32 @@
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K252" s="12" t="inlineStr">
@@ -14592,7 +14576,7 @@
       </c>
       <c r="N252" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14586,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14617,32 +14601,32 @@
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K253" s="12" t="inlineStr">
@@ -14662,7 +14646,7 @@
       </c>
       <c r="N253" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14656,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14687,32 +14671,32 @@
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K254" s="12" t="inlineStr">
@@ -14722,27 +14706,27 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N254" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="60" customHeight="1">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14752,27 +14736,39 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H255" s="2" t="inlineStr"/>
-      <c r="I255" s="5" t="inlineStr"/>
-      <c r="J255" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I255" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J255" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K255" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14780,15 +14776,19 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N255" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N255" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="45" customHeight="1">
       <c r="A256" s="2" t="n">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
@@ -14806,22 +14806,22 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
@@ -14844,13 +14844,13 @@
       </c>
       <c r="N256" s="8" t="inlineStr"/>
     </row>
-    <row r="257" ht="60" customHeight="1">
+    <row r="257" ht="45" customHeight="1">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
@@ -14860,22 +14860,22 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
@@ -14888,23 +14888,23 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N257" s="8" t="inlineStr"/>
     </row>
-    <row r="258" ht="150" customHeight="1">
+    <row r="258" ht="60" customHeight="1">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
@@ -14914,31 +14914,27 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
       <c r="I258" s="5" t="inlineStr"/>
-      <c r="J258" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J258" s="5" t="inlineStr"/>
       <c r="K258" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14946,27 +14942,23 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N258" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="105" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N258" s="8" t="inlineStr"/>
+    </row>
+    <row r="259" ht="150" customHeight="1">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -14976,27 +14968,31 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
       <c r="I259" s="5" t="inlineStr"/>
-      <c r="J259" s="5" t="inlineStr"/>
+      <c r="J259" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K259" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15004,23 +15000,27 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
-        </is>
-      </c>
-      <c r="N259" s="8" t="inlineStr"/>
-    </row>
-    <row r="260" ht="45" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N259" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="105" customHeight="1">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -15030,22 +15030,22 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
@@ -15058,12 +15058,12 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N260" s="8" t="inlineStr"/>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -15089,17 +15089,17 @@
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
@@ -15143,17 +15143,17 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
@@ -15197,17 +15197,17 @@
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15251,17 +15251,17 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15305,17 +15305,17 @@
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15467,17 +15467,17 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15521,17 +15521,17 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15575,17 +15575,17 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -15662,13 +15662,13 @@
       </c>
       <c r="N271" s="8" t="inlineStr"/>
     </row>
-    <row r="272" ht="60" customHeight="1">
+    <row r="272" ht="45" customHeight="1">
       <c r="A272" s="2" t="n">
         <v>271</v>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15678,22 +15678,22 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
@@ -15706,23 +15706,23 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N272" s="8" t="inlineStr"/>
     </row>
-    <row r="273" ht="120" customHeight="1">
+    <row r="273" ht="60" customHeight="1">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15732,39 +15732,27 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H273" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I273" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J273" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr"/>
+      <c r="I273" s="5" t="inlineStr"/>
+      <c r="J273" s="5" t="inlineStr"/>
       <c r="K273" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15772,27 +15760,23 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N273" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="75" customHeight="1">
+          <t>cf702f2b4</t>
+        </is>
+      </c>
+      <c r="N273" s="8" t="inlineStr"/>
+    </row>
+    <row r="274" ht="120" customHeight="1">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15802,27 +15786,39 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H274" s="2" t="inlineStr"/>
-      <c r="I274" s="5" t="inlineStr"/>
-      <c r="J274" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I274" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J274" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K274" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15830,23 +15826,27 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N274" s="8" t="inlineStr"/>
-    </row>
-    <row r="275" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N274" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="75" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15856,22 +15856,22 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -15884,23 +15884,23 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N275" s="8" t="inlineStr"/>
     </row>
-    <row r="276" ht="45" customHeight="1">
+    <row r="276" ht="60" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15915,17 +15915,17 @@
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -15948,13 +15948,13 @@
       </c>
       <c r="N276" s="8" t="inlineStr"/>
     </row>
-    <row r="277" ht="60" customHeight="1">
+    <row r="277" ht="45" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15969,17 +15969,17 @@
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
@@ -16002,13 +16002,13 @@
       </c>
       <c r="N277" s="8" t="inlineStr"/>
     </row>
-    <row r="278" ht="45" customHeight="1">
+    <row r="278" ht="60" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -16023,17 +16023,17 @@
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -16051,7 +16051,7 @@
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N278" s="8" t="inlineStr"/>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -16077,17 +16077,17 @@
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -16110,13 +16110,13 @@
       </c>
       <c r="N279" s="8" t="inlineStr"/>
     </row>
-    <row r="280" ht="120" customHeight="1">
+    <row r="280" ht="45" customHeight="1">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16126,22 +16126,22 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -16154,23 +16154,23 @@
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N280" s="8" t="inlineStr"/>
     </row>
-    <row r="281" ht="60" customHeight="1">
+    <row r="281" ht="120" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16180,22 +16180,22 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
@@ -16208,23 +16208,23 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>93ec11842</t>
         </is>
       </c>
       <c r="N281" s="8" t="inlineStr"/>
     </row>
-    <row r="282" ht="105" customHeight="1">
+    <row r="282" ht="60" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16234,31 +16234,27 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
       <c r="I282" s="5" t="inlineStr"/>
-      <c r="J282" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J282" s="5" t="inlineStr"/>
       <c r="K282" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16266,27 +16262,23 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N282" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="135" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N282" s="8" t="inlineStr"/>
+    </row>
+    <row r="283" ht="105" customHeight="1">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16296,37 +16288,29 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H283" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I283" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr"/>
+      <c r="I283" s="5" t="inlineStr"/>
       <c r="J283" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K283" s="12" t="inlineStr">
@@ -16336,27 +16320,27 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N283" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="135" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16366,27 +16350,39 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H284" s="2" t="inlineStr"/>
-      <c r="I284" s="5" t="inlineStr"/>
-      <c r="J284" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I284" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J284" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K284" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16394,23 +16390,27 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N284" s="8" t="inlineStr"/>
-    </row>
-    <row r="285" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N284" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="45" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16420,31 +16420,27 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr"/>
       <c r="I285" s="5" t="inlineStr"/>
-      <c r="J285" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J285" s="5" t="inlineStr"/>
       <c r="K285" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16452,27 +16448,23 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N285" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N285" s="8" t="inlineStr"/>
+    </row>
+    <row r="286" ht="120" customHeight="1">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16482,27 +16474,31 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr"/>
       <c r="I286" s="5" t="inlineStr"/>
-      <c r="J286" s="5" t="inlineStr"/>
+      <c r="J286" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K286" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16510,15 +16506,19 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N286" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N286" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="60" customHeight="1">
       <c r="A287" s="2" t="n">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C287" s="10" t="inlineStr">
@@ -16536,22 +16536,22 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr"/>
@@ -16569,60 +16569,48 @@
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N287" s="8" t="inlineStr"/>
     </row>
-    <row r="288" ht="45" customHeight="1">
+    <row r="288" ht="60" customHeight="1">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C288" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C288" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H288" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I288" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J288" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="5" t="inlineStr"/>
+      <c r="J288" s="5" t="inlineStr"/>
       <c r="K288" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16630,15 +16618,15 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M288" s="3" t="inlineStr"/>
-      <c r="N288" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N288" s="8" t="inlineStr"/>
     </row>
     <row r="289" ht="45" customHeight="1">
       <c r="A289" s="2" t="n">
@@ -16646,7 +16634,7 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
@@ -16661,32 +16649,32 @@
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J289" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K289" s="12" t="inlineStr">
@@ -16702,7 +16690,7 @@
       <c r="M289" s="3" t="inlineStr"/>
       <c r="N289" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16700,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
@@ -16722,35 +16710,39 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J290" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J290" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K290" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16758,17 +16750,13 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M290" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr"/>
       <c r="N290" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -16778,59 +16766,63 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C291" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C291" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J291" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K291" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L291" s="2" t="inlineStr"/>
-      <c r="M291" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J291" s="5" t="inlineStr"/>
+      <c r="K291" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N291" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16832,7 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C292" s="10" t="inlineStr">
@@ -16850,37 +16842,37 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J292" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K292" s="14" t="inlineStr">
@@ -16902,109 +16894,109 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C293" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C293" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K293" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K293" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L293" s="2" t="inlineStr"/>
       <c r="M293" s="3" t="inlineStr"/>
       <c r="N293" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="45" customHeight="1">
       <c r="A294" s="2" t="n">
         <v>293</v>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C294" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K294" s="15" t="inlineStr">
@@ -17012,147 +17004,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L294" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L294" s="2" t="inlineStr"/>
       <c r="M294" s="3" t="inlineStr"/>
       <c r="N294" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="75" customHeight="1">
       <c r="A295" s="2" t="n">
         <v>294</v>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E295" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I295" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J295" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K295" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr"/>
+      <c r="N295" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="195" customHeight="1">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C295" s="10" t="inlineStr">
+      <c r="C296" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G295" s="5" t="inlineStr">
+      <c r="G296" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H295" s="2" t="inlineStr">
+      <c r="H296" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J295" s="5" t="inlineStr">
+      <c r="J296" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K295" s="15" t="inlineStr">
+      <c r="K296" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L295" s="2" t="inlineStr">
+      <c r="L296" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M295" s="3" t="inlineStr"/>
-      <c r="N295" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="90" customHeight="1">
-      <c r="A296" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="B296" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C296" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E296" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H296" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I296" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J296" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K296" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L296" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M296" s="3" t="inlineStr"/>
       <c r="N296" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="90" customHeight="1">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C297" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E297" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I297" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J297" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K297" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M297" s="3" t="inlineStr"/>
+      <c r="N297" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -17257,10 +17311,10 @@
         <v>86</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
@@ -17314,10 +17368,10 @@
         <v>111</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-15.xlsx
+++ b/cache/open_items_2026-06-15.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N297"/>
+  <dimension ref="A1:N298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12440,13 +12440,13 @@
       </c>
       <c r="N214" s="8" t="inlineStr"/>
     </row>
-    <row r="215" ht="60" customHeight="1">
+    <row r="215" ht="105" customHeight="1">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>BULLALGO-1</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12456,22 +12456,22 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>BullVeda</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>BullAlgo — transparent LuxAlgo-style overlays + MCDX + Price Action</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>Ownable, inspectable reproduction of LuxAlgo Signals&amp;Overlays + Price Action Concepts + MCDX, replacing the TradingView black box; every layer is a standard auditable indicator</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>bullalgo.py engines (Confirmation/Signals-Overlays screener/PAC screener/chart-series/PAC-chart/MCDX); server.py 4 endpoints /api/bullalgo/*; pattern_data SWING_1H mode; isolated test benches bullalgo-test.html + setup-tv-lab.html; PRODUCTION Overview integration in lens-overview.jsx (OverviewMcdx synced strip + interactive/expand setup chart + Setup&lt;-&gt;PriceAction toggle). Display-only, real data, NOT identical to LuxAlgo (transparent approximation)</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12484,23 +12484,23 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>296777349</t>
         </is>
       </c>
       <c r="N215" s="8" t="inlineStr"/>
     </row>
-    <row r="216" ht="45" customHeight="1">
+    <row r="216" ht="60" customHeight="1">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12510,22 +12510,22 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12564,22 +12564,22 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12592,12 +12592,12 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N217" s="8" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -12947,17 +12947,17 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N224" s="8" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13590,22 +13590,22 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13618,23 +13618,23 @@
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N236" s="8" t="inlineStr"/>
     </row>
-    <row r="237" ht="105" customHeight="1">
+    <row r="237" ht="45" customHeight="1">
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13677,18 +13677,18 @@
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N237" s="8" t="inlineStr"/>
     </row>
-    <row r="238" ht="75" customHeight="1">
+    <row r="238" ht="105" customHeight="1">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-T1CAT-1</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13698,22 +13698,22 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>T1 CATALYST pill read wrong field</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13726,12 +13726,12 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N238" s="8" t="inlineStr"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>SCANNER-T1CAT-1</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13752,22 +13752,22 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>T1 CATALYST pill read wrong field</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -13780,12 +13780,12 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N239" s="8" t="inlineStr"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -13806,22 +13806,22 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
@@ -13834,23 +13834,23 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>613f10e35</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N240" s="8" t="inlineStr"/>
     </row>
-    <row r="241" ht="60" customHeight="1">
+    <row r="241" ht="75" customHeight="1">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -13860,22 +13860,22 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr"/>
@@ -13888,12 +13888,12 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>613f10e35</t>
         </is>
       </c>
       <c r="N241" s="8" t="inlineStr"/>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -13914,34 +13914,26 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I242" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr"/>
+      <c r="I242" s="5" t="inlineStr"/>
       <c r="J242" s="5" t="inlineStr"/>
       <c r="K242" s="12" t="inlineStr">
         <is>
@@ -13950,27 +13942,23 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N242" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N242" s="8" t="inlineStr"/>
+    </row>
+    <row r="243" ht="60" customHeight="1">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -13985,17 +13973,17 @@
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -14005,14 +13993,10 @@
       </c>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J243" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J243" s="5" t="inlineStr"/>
       <c r="K243" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14025,12 +14009,12 @@
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N243" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14024,7 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14055,22 +14039,34 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr"/>
-      <c r="I244" s="5" t="inlineStr"/>
-      <c r="J244" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I244" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J244" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K244" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14078,23 +14074,27 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N244" s="8" t="inlineStr"/>
-    </row>
-    <row r="245" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N244" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="75" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14104,22 +14104,22 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr"/>
@@ -14132,23 +14132,23 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N245" s="8" t="inlineStr"/>
     </row>
-    <row r="246" ht="45" customHeight="1">
+    <row r="246" ht="60" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14158,34 +14158,26 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I246" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="5" t="inlineStr"/>
       <c r="J246" s="5" t="inlineStr"/>
       <c r="K246" s="12" t="inlineStr">
         <is>
@@ -14194,27 +14186,23 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N246" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="90" customHeight="1">
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N246" s="8" t="inlineStr"/>
+    </row>
+    <row r="247" ht="45" customHeight="1">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14224,26 +14212,34 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="inlineStr"/>
-      <c r="I247" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I247" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J247" s="5" t="inlineStr"/>
       <c r="K247" s="12" t="inlineStr">
         <is>
@@ -14252,23 +14248,27 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N247" s="8" t="inlineStr"/>
-    </row>
-    <row r="248" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N247" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="90" customHeight="1">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14278,39 +14278,27 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I248" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J248" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="5" t="inlineStr"/>
+      <c r="J248" s="5" t="inlineStr"/>
       <c r="K248" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14318,19 +14306,15 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N248" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N248" s="8" t="inlineStr"/>
     </row>
     <row r="249" ht="45" customHeight="1">
       <c r="A249" s="2" t="n">
@@ -14338,7 +14322,7 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14348,27 +14332,39 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="inlineStr"/>
-      <c r="I249" s="5" t="inlineStr"/>
-      <c r="J249" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I249" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J249" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K249" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14376,15 +14372,19 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N249" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N249" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="45" customHeight="1">
       <c r="A250" s="2" t="n">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14402,22 +14402,22 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr"/>
@@ -14435,18 +14435,18 @@
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N250" s="8" t="inlineStr"/>
     </row>
-    <row r="251" ht="75" customHeight="1">
+    <row r="251" ht="45" customHeight="1">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14456,39 +14456,27 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I251" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J251" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr"/>
+      <c r="I251" s="5" t="inlineStr"/>
+      <c r="J251" s="5" t="inlineStr"/>
       <c r="K251" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14496,27 +14484,23 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N251" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N251" s="8" t="inlineStr"/>
+    </row>
+    <row r="252" ht="75" customHeight="1">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14526,37 +14510,37 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K252" s="12" t="inlineStr">
@@ -14566,17 +14550,17 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N252" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14570,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14601,32 +14585,32 @@
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K253" s="12" t="inlineStr">
@@ -14646,7 +14630,7 @@
       </c>
       <c r="N253" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -14656,7 +14640,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14671,32 +14655,32 @@
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K254" s="12" t="inlineStr">
@@ -14716,7 +14700,7 @@
       </c>
       <c r="N254" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14710,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14741,32 +14725,32 @@
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J255" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K255" s="12" t="inlineStr">
@@ -14776,27 +14760,27 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N255" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="60" customHeight="1">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
@@ -14806,27 +14790,39 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="inlineStr"/>
-      <c r="I256" s="5" t="inlineStr"/>
-      <c r="J256" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I256" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J256" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K256" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14834,15 +14830,19 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N256" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N256" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="45" customHeight="1">
       <c r="A257" s="2" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
@@ -14860,22 +14860,22 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
@@ -14898,13 +14898,13 @@
       </c>
       <c r="N257" s="8" t="inlineStr"/>
     </row>
-    <row r="258" ht="60" customHeight="1">
+    <row r="258" ht="45" customHeight="1">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
@@ -14914,22 +14914,22 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
@@ -14942,23 +14942,23 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N258" s="8" t="inlineStr"/>
     </row>
-    <row r="259" ht="150" customHeight="1">
+    <row r="259" ht="60" customHeight="1">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -14968,31 +14968,27 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
       <c r="I259" s="5" t="inlineStr"/>
-      <c r="J259" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J259" s="5" t="inlineStr"/>
       <c r="K259" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15000,27 +14996,23 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N259" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="105" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N259" s="8" t="inlineStr"/>
+    </row>
+    <row r="260" ht="150" customHeight="1">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -15030,27 +15022,31 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
       <c r="I260" s="5" t="inlineStr"/>
-      <c r="J260" s="5" t="inlineStr"/>
+      <c r="J260" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K260" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15058,23 +15054,27 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
-        </is>
-      </c>
-      <c r="N260" s="8" t="inlineStr"/>
-    </row>
-    <row r="261" ht="45" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N260" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="105" customHeight="1">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -15084,22 +15084,22 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -15112,12 +15112,12 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N261" s="8" t="inlineStr"/>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
@@ -15143,17 +15143,17 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
@@ -15197,17 +15197,17 @@
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15251,17 +15251,17 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15305,17 +15305,17 @@
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15467,17 +15467,17 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15521,17 +15521,17 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15575,17 +15575,17 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15683,17 +15683,17 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
@@ -15716,13 +15716,13 @@
       </c>
       <c r="N272" s="8" t="inlineStr"/>
     </row>
-    <row r="273" ht="60" customHeight="1">
+    <row r="273" ht="45" customHeight="1">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15732,22 +15732,22 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
@@ -15760,23 +15760,23 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N273" s="8" t="inlineStr"/>
     </row>
-    <row r="274" ht="120" customHeight="1">
+    <row r="274" ht="60" customHeight="1">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15786,39 +15786,27 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H274" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I274" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J274" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="5" t="inlineStr"/>
+      <c r="J274" s="5" t="inlineStr"/>
       <c r="K274" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15826,27 +15814,23 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N274" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="75" customHeight="1">
+          <t>cf702f2b4</t>
+        </is>
+      </c>
+      <c r="N274" s="8" t="inlineStr"/>
+    </row>
+    <row r="275" ht="120" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15856,27 +15840,39 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H275" s="2" t="inlineStr"/>
-      <c r="I275" s="5" t="inlineStr"/>
-      <c r="J275" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I275" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J275" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K275" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15884,23 +15880,27 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N275" s="8" t="inlineStr"/>
-    </row>
-    <row r="276" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N275" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="75" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15910,22 +15910,22 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -15938,23 +15938,23 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N276" s="8" t="inlineStr"/>
     </row>
-    <row r="277" ht="45" customHeight="1">
+    <row r="277" ht="60" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15969,17 +15969,17 @@
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
@@ -16002,13 +16002,13 @@
       </c>
       <c r="N277" s="8" t="inlineStr"/>
     </row>
-    <row r="278" ht="60" customHeight="1">
+    <row r="278" ht="45" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -16023,17 +16023,17 @@
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -16056,13 +16056,13 @@
       </c>
       <c r="N278" s="8" t="inlineStr"/>
     </row>
-    <row r="279" ht="45" customHeight="1">
+    <row r="279" ht="60" customHeight="1">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -16077,17 +16077,17 @@
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N279" s="8" t="inlineStr"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16131,17 +16131,17 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -16164,13 +16164,13 @@
       </c>
       <c r="N280" s="8" t="inlineStr"/>
     </row>
-    <row r="281" ht="120" customHeight="1">
+    <row r="281" ht="45" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16180,22 +16180,22 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
@@ -16208,23 +16208,23 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N281" s="8" t="inlineStr"/>
     </row>
-    <row r="282" ht="60" customHeight="1">
+    <row r="282" ht="120" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16234,22 +16234,22 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
@@ -16262,23 +16262,23 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>93ec11842</t>
         </is>
       </c>
       <c r="N282" s="8" t="inlineStr"/>
     </row>
-    <row r="283" ht="105" customHeight="1">
+    <row r="283" ht="60" customHeight="1">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16288,31 +16288,27 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr"/>
       <c r="I283" s="5" t="inlineStr"/>
-      <c r="J283" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J283" s="5" t="inlineStr"/>
       <c r="K283" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16320,27 +16316,23 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N283" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="135" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N283" s="8" t="inlineStr"/>
+    </row>
+    <row r="284" ht="105" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16350,37 +16342,29 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H284" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I284" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr"/>
+      <c r="I284" s="5" t="inlineStr"/>
       <c r="J284" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K284" s="12" t="inlineStr">
@@ -16390,27 +16374,27 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N284" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="135" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16420,27 +16404,39 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H285" s="2" t="inlineStr"/>
-      <c r="I285" s="5" t="inlineStr"/>
-      <c r="J285" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I285" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J285" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K285" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16448,23 +16444,27 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N285" s="8" t="inlineStr"/>
-    </row>
-    <row r="286" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N285" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="45" customHeight="1">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16474,31 +16474,27 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr"/>
       <c r="I286" s="5" t="inlineStr"/>
-      <c r="J286" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J286" s="5" t="inlineStr"/>
       <c r="K286" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16506,27 +16502,23 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N286" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="287" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N286" s="8" t="inlineStr"/>
+    </row>
+    <row r="287" ht="120" customHeight="1">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C287" s="10" t="inlineStr">
@@ -16536,27 +16528,31 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr"/>
       <c r="I287" s="5" t="inlineStr"/>
-      <c r="J287" s="5" t="inlineStr"/>
+      <c r="J287" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K287" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16564,15 +16560,19 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N287" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N287" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="60" customHeight="1">
       <c r="A288" s="2" t="n">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C288" s="10" t="inlineStr">
@@ -16590,22 +16590,22 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr"/>
@@ -16623,60 +16623,48 @@
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N288" s="8" t="inlineStr"/>
     </row>
-    <row r="289" ht="45" customHeight="1">
+    <row r="289" ht="60" customHeight="1">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C289" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C289" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H289" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I289" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J289" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr"/>
+      <c r="I289" s="5" t="inlineStr"/>
+      <c r="J289" s="5" t="inlineStr"/>
       <c r="K289" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16684,15 +16672,15 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M289" s="3" t="inlineStr"/>
-      <c r="N289" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N289" s="8" t="inlineStr"/>
     </row>
     <row r="290" ht="45" customHeight="1">
       <c r="A290" s="2" t="n">
@@ -16700,7 +16688,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
@@ -16715,32 +16703,32 @@
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J290" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K290" s="12" t="inlineStr">
@@ -16756,7 +16744,7 @@
       <c r="M290" s="3" t="inlineStr"/>
       <c r="N290" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -16766,7 +16754,7 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -16776,35 +16764,39 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J291" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J291" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K291" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16812,17 +16804,13 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M291" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M291" s="3" t="inlineStr"/>
       <c r="N291" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -16832,59 +16820,63 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C292" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C292" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J292" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K292" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L292" s="2" t="inlineStr"/>
-      <c r="M292" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J292" s="5" t="inlineStr"/>
+      <c r="K292" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N292" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -16894,7 +16886,7 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C293" s="10" t="inlineStr">
@@ -16904,37 +16896,37 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K293" s="14" t="inlineStr">
@@ -16956,109 +16948,109 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C294" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C294" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K294" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K294" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L294" s="2" t="inlineStr"/>
       <c r="M294" s="3" t="inlineStr"/>
       <c r="N294" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="45" customHeight="1">
       <c r="A295" s="2" t="n">
         <v>294</v>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C295" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J295" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K295" s="15" t="inlineStr">
@@ -17066,147 +17058,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L295" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L295" s="2" t="inlineStr"/>
       <c r="M295" s="3" t="inlineStr"/>
       <c r="N295" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="75" customHeight="1">
       <c r="A296" s="2" t="n">
         <v>295</v>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C296" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E296" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I296" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J296" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K296" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr"/>
+      <c r="N296" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="195" customHeight="1">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C296" s="10" t="inlineStr">
+      <c r="C297" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G296" s="5" t="inlineStr">
+      <c r="G297" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H296" s="2" t="inlineStr">
+      <c r="H297" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J296" s="5" t="inlineStr">
+      <c r="J297" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K296" s="15" t="inlineStr">
+      <c r="K297" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L296" s="2" t="inlineStr">
+      <c r="L297" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M296" s="3" t="inlineStr"/>
-      <c r="N296" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="90" customHeight="1">
-      <c r="A297" s="2" t="n">
-        <v>296</v>
-      </c>
-      <c r="B297" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C297" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E297" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H297" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I297" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J297" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K297" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L297" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M297" s="3" t="inlineStr"/>
       <c r="N297" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="90" customHeight="1">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C298" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E298" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I298" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J298" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K298" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M298" s="3" t="inlineStr"/>
+      <c r="N298" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -17311,10 +17365,10 @@
         <v>86</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
@@ -17368,10 +17422,10 @@
         <v>111</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-15.xlsx
+++ b/cache/open_items_2026-06-15.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N298"/>
+  <dimension ref="A1:N299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>TE-SESSION-CACHE</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16288,22 +16288,22 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Structural Targets</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>Session-date cache invalidation</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr"/>
@@ -16316,23 +16316,23 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>33146be5e</t>
         </is>
       </c>
       <c r="N283" s="8" t="inlineStr"/>
     </row>
-    <row r="284" ht="105" customHeight="1">
+    <row r="284" ht="60" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16342,31 +16342,27 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
       <c r="I284" s="5" t="inlineStr"/>
-      <c r="J284" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J284" s="5" t="inlineStr"/>
       <c r="K284" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16374,27 +16370,23 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N284" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="135" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N284" s="8" t="inlineStr"/>
+    </row>
+    <row r="285" ht="105" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16404,37 +16396,29 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H285" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I285" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr"/>
+      <c r="I285" s="5" t="inlineStr"/>
       <c r="J285" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K285" s="12" t="inlineStr">
@@ -16444,27 +16428,27 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N285" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="135" customHeight="1">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16474,27 +16458,39 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H286" s="2" t="inlineStr"/>
-      <c r="I286" s="5" t="inlineStr"/>
-      <c r="J286" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I286" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J286" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K286" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16502,23 +16498,27 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N286" s="8" t="inlineStr"/>
-    </row>
-    <row r="287" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N286" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="45" customHeight="1">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C287" s="10" t="inlineStr">
@@ -16528,31 +16528,27 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr"/>
       <c r="I287" s="5" t="inlineStr"/>
-      <c r="J287" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J287" s="5" t="inlineStr"/>
       <c r="K287" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16560,27 +16556,23 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N287" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N287" s="8" t="inlineStr"/>
+    </row>
+    <row r="288" ht="120" customHeight="1">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C288" s="10" t="inlineStr">
@@ -16590,27 +16582,31 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr"/>
       <c r="I288" s="5" t="inlineStr"/>
-      <c r="J288" s="5" t="inlineStr"/>
+      <c r="J288" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K288" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16618,15 +16614,19 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N288" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N288" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="60" customHeight="1">
       <c r="A289" s="2" t="n">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C289" s="10" t="inlineStr">
@@ -16644,22 +16644,22 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr"/>
@@ -16677,60 +16677,48 @@
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N289" s="8" t="inlineStr"/>
     </row>
-    <row r="290" ht="45" customHeight="1">
+    <row r="290" ht="60" customHeight="1">
       <c r="A290" s="2" t="n">
         <v>289</v>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C290" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C290" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H290" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I290" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J290" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="5" t="inlineStr"/>
+      <c r="J290" s="5" t="inlineStr"/>
       <c r="K290" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16738,15 +16726,15 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M290" s="3" t="inlineStr"/>
-      <c r="N290" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N290" s="8" t="inlineStr"/>
     </row>
     <row r="291" ht="45" customHeight="1">
       <c r="A291" s="2" t="n">
@@ -16754,7 +16742,7 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -16769,32 +16757,32 @@
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K291" s="12" t="inlineStr">
@@ -16810,7 +16798,7 @@
       <c r="M291" s="3" t="inlineStr"/>
       <c r="N291" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16808,7 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -16830,35 +16818,39 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J292" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J292" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K292" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16866,17 +16858,13 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M292" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M292" s="3" t="inlineStr"/>
       <c r="N292" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -16886,59 +16874,63 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C293" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C293" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J293" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K293" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L293" s="2" t="inlineStr"/>
-      <c r="M293" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J293" s="5" t="inlineStr"/>
+      <c r="K293" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N293" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16940,7 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C294" s="10" t="inlineStr">
@@ -16958,37 +16950,37 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K294" s="14" t="inlineStr">
@@ -17010,109 +17002,109 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C295" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C295" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J295" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K295" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K295" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L295" s="2" t="inlineStr"/>
       <c r="M295" s="3" t="inlineStr"/>
       <c r="N295" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="45" customHeight="1">
       <c r="A296" s="2" t="n">
         <v>295</v>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C296" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J296" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K296" s="15" t="inlineStr">
@@ -17120,147 +17112,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L296" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="3" t="inlineStr"/>
       <c r="N296" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="75" customHeight="1">
       <c r="A297" s="2" t="n">
         <v>296</v>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C297" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E297" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I297" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J297" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K297" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M297" s="3" t="inlineStr"/>
+      <c r="N297" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="195" customHeight="1">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C297" s="10" t="inlineStr">
+      <c r="C298" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G297" s="5" t="inlineStr">
+      <c r="G298" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H297" s="2" t="inlineStr">
+      <c r="H298" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J297" s="5" t="inlineStr">
+      <c r="J298" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K297" s="15" t="inlineStr">
+      <c r="K298" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L297" s="2" t="inlineStr">
+      <c r="L298" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M297" s="3" t="inlineStr"/>
-      <c r="N297" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="90" customHeight="1">
-      <c r="A298" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="B298" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C298" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E298" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H298" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I298" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J298" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K298" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L298" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M298" s="3" t="inlineStr"/>
       <c r="N298" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="90" customHeight="1">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C299" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E299" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I299" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J299" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K299" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M299" s="3" t="inlineStr"/>
+      <c r="N299" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -17365,10 +17419,10 @@
         <v>86</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5">
@@ -17422,10 +17476,10 @@
         <v>111</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-15.xlsx
+++ b/cache/open_items_2026-06-15.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N299"/>
+  <dimension ref="A1:N301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12494,13 +12494,13 @@
       </c>
       <c r="N215" s="8" t="inlineStr"/>
     </row>
-    <row r="216" ht="60" customHeight="1">
+    <row r="216" ht="75" customHeight="1">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>BULLALGO-FOOTPRINT</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12510,22 +12510,22 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>BullVeda Lenses</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>Real institutional footprint strip</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>MCDX is interpretive momentum math (no order flow); users asked why we cant show real smart-money detail</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>Added /api/bullalgo/{t}/footprint + bullalgo.footprint() aggregating REAL attributable signals: OBV/AD accumulation (live), insider Form 4 net (SEC, value-filtered), 13F institutional holders + QoQ change (EODHD). Rendered as honest counterpart strip under MCDX. No new data license.</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12538,23 +12538,23 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>b3314aaf2</t>
         </is>
       </c>
       <c r="N216" s="8" t="inlineStr"/>
     </row>
-    <row r="217" ht="45" customHeight="1">
+    <row r="217" ht="60" customHeight="1">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>BULLALGO-LENS</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12564,22 +12564,22 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>BullVeda Lenses</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>BullAlgo native lens + MCDX alignment</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>Ported bullalgo-test.html prototype into a native per-ticker lens (16th, in-house LuxAlgo replacement for removed tv lens); MCDX money-flow misaligned with price chart</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>lens-bullalgo.jsx + lens-bullalgo.css scoped; registered in LENSES/detail-panel/dev-loader/CapStudio; backend mcdx_series emits whitespace warmup points so bar counts match (180==180) + minimumWidth:64 on both price scales</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12592,23 +12592,23 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>b3314aaf2</t>
         </is>
       </c>
       <c r="N217" s="8" t="inlineStr"/>
     </row>
-    <row r="218" ht="45" customHeight="1">
+    <row r="218" ht="60" customHeight="1">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12618,22 +12618,22 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12646,12 +12646,12 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N218" s="8" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12672,22 +12672,22 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -12700,12 +12700,12 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N219" s="8" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13001,17 +13001,17 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N225" s="8" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13055,17 +13055,17 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N226" s="8" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13672,23 +13672,23 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N237" s="8" t="inlineStr"/>
     </row>
-    <row r="238" ht="105" customHeight="1">
+    <row r="238" ht="45" customHeight="1">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13698,22 +13698,22 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13726,23 +13726,23 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N238" s="8" t="inlineStr"/>
     </row>
-    <row r="239" ht="75" customHeight="1">
+    <row r="239" ht="45" customHeight="1">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-T1CAT-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13752,22 +13752,22 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>T1 CATALYST pill read wrong field</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -13780,23 +13780,23 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N239" s="8" t="inlineStr"/>
     </row>
-    <row r="240" ht="75" customHeight="1">
+    <row r="240" ht="105" customHeight="1">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -13806,22 +13806,22 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
@@ -13834,12 +13834,12 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N240" s="8" t="inlineStr"/>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>SCANNER-T1CAT-1</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -13860,22 +13860,22 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>T1 CATALYST pill read wrong field</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr"/>
@@ -13893,18 +13893,18 @@
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>613f10e35</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N241" s="8" t="inlineStr"/>
     </row>
-    <row r="242" ht="60" customHeight="1">
+    <row r="242" ht="75" customHeight="1">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -13914,22 +13914,22 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr"/>
@@ -13942,23 +13942,23 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N242" s="8" t="inlineStr"/>
     </row>
-    <row r="243" ht="60" customHeight="1">
+    <row r="243" ht="75" customHeight="1">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -13968,34 +13968,26 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr"/>
+      <c r="I243" s="5" t="inlineStr"/>
       <c r="J243" s="5" t="inlineStr"/>
       <c r="K243" s="12" t="inlineStr">
         <is>
@@ -14004,27 +13996,23 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N243" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="75" customHeight="1">
+          <t>613f10e35</t>
+        </is>
+      </c>
+      <c r="N243" s="8" t="inlineStr"/>
+    </row>
+    <row r="244" ht="60" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14034,39 +14022,27 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I244" s="5" t="inlineStr">
-        <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J244" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="5" t="inlineStr"/>
+      <c r="J244" s="5" t="inlineStr"/>
       <c r="K244" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14074,27 +14050,23 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N244" s="8" t="inlineStr">
-        <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N244" s="8" t="inlineStr"/>
+    </row>
+    <row r="245" ht="60" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14109,21 +14081,29 @@
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H245" s="2" t="inlineStr"/>
-      <c r="I245" s="5" t="inlineStr"/>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I245" s="5" t="inlineStr">
+        <is>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
       <c r="J245" s="5" t="inlineStr"/>
       <c r="K245" s="12" t="inlineStr">
         <is>
@@ -14132,23 +14112,27 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N245" s="8" t="inlineStr"/>
-    </row>
-    <row r="246" ht="60" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N245" s="8" t="inlineStr">
+        <is>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="75" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14158,27 +14142,39 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr"/>
-      <c r="I246" s="5" t="inlineStr"/>
-      <c r="J246" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I246" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J246" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K246" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14186,23 +14182,27 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N246" s="8" t="inlineStr"/>
-    </row>
-    <row r="247" ht="45" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N246" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="75" customHeight="1">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14212,34 +14212,26 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I247" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr"/>
+      <c r="I247" s="5" t="inlineStr"/>
       <c r="J247" s="5" t="inlineStr"/>
       <c r="K247" s="12" t="inlineStr">
         <is>
@@ -14248,27 +14240,23 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N247" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="90" customHeight="1">
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N247" s="8" t="inlineStr"/>
+    </row>
+    <row r="248" ht="60" customHeight="1">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14278,22 +14266,22 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr"/>
@@ -14322,7 +14310,7 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14332,39 +14320,35 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J249" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J249" s="5" t="inlineStr"/>
       <c r="K249" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14372,27 +14356,27 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N249" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="45" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="90" customHeight="1">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14402,22 +14386,22 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr"/>
@@ -14430,12 +14414,12 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N250" s="8" t="inlineStr"/>
@@ -14446,7 +14430,7 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14456,27 +14440,39 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr"/>
-      <c r="I251" s="5" t="inlineStr"/>
-      <c r="J251" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I251" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J251" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K251" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14484,23 +14480,27 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N251" s="8" t="inlineStr"/>
-    </row>
-    <row r="252" ht="75" customHeight="1">
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N251" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="45" customHeight="1">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14510,39 +14510,27 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H252" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I252" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J252" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr"/>
+      <c r="I252" s="5" t="inlineStr"/>
+      <c r="J252" s="5" t="inlineStr"/>
       <c r="K252" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14550,27 +14538,23 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N252" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="60" customHeight="1">
+          <t>d1ea97913</t>
+        </is>
+      </c>
+      <c r="N252" s="8" t="inlineStr"/>
+    </row>
+    <row r="253" ht="45" customHeight="1">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14580,39 +14564,27 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
-        </is>
-      </c>
-      <c r="H253" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I253" s="5" t="inlineStr">
-        <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J253" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr"/>
+      <c r="I253" s="5" t="inlineStr"/>
+      <c r="J253" s="5" t="inlineStr"/>
       <c r="K253" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14620,27 +14592,23 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N253" s="8" t="inlineStr">
-        <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N253" s="8" t="inlineStr"/>
+    </row>
+    <row r="254" ht="75" customHeight="1">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14650,37 +14618,37 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K254" s="12" t="inlineStr">
@@ -14690,17 +14658,17 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N254" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14678,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14725,32 +14693,32 @@
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J255" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K255" s="12" t="inlineStr">
@@ -14770,7 +14738,7 @@
       </c>
       <c r="N255" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14748,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
@@ -14795,32 +14763,32 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J256" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K256" s="12" t="inlineStr">
@@ -14830,27 +14798,27 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N256" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="45" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="60" customHeight="1">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
@@ -14860,27 +14828,39 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H257" s="2" t="inlineStr"/>
-      <c r="I257" s="5" t="inlineStr"/>
-      <c r="J257" s="5" t="inlineStr"/>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I257" s="5" t="inlineStr">
+        <is>
+          <t>Win: visibility into RBAC changes.</t>
+        </is>
+      </c>
+      <c r="J257" s="5" t="inlineStr">
+        <is>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+        </is>
+      </c>
       <c r="K257" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14888,23 +14868,27 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N257" s="8" t="inlineStr"/>
-    </row>
-    <row r="258" ht="45" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N257" s="8" t="inlineStr">
+        <is>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="60" customHeight="1">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
@@ -14914,27 +14898,39 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
-        </is>
-      </c>
-      <c r="H258" s="2" t="inlineStr"/>
-      <c r="I258" s="5" t="inlineStr"/>
-      <c r="J258" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I258" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J258" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K258" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14942,23 +14938,27 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N258" s="8" t="inlineStr"/>
-    </row>
-    <row r="259" ht="60" customHeight="1">
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N258" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="45" customHeight="1">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -14968,22 +14968,22 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
@@ -14996,23 +14996,23 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N259" s="8" t="inlineStr"/>
     </row>
-    <row r="260" ht="150" customHeight="1">
+    <row r="260" ht="45" customHeight="1">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -15022,31 +15022,27 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
       <c r="I260" s="5" t="inlineStr"/>
-      <c r="J260" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J260" s="5" t="inlineStr"/>
       <c r="K260" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15054,27 +15050,23 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N260" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="105" customHeight="1">
+          <t>0dc7675ee</t>
+        </is>
+      </c>
+      <c r="N260" s="8" t="inlineStr"/>
+    </row>
+    <row r="261" ht="60" customHeight="1">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -15084,22 +15076,22 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -15112,23 +15104,23 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
+          <t>15f8f9600</t>
         </is>
       </c>
       <c r="N261" s="8" t="inlineStr"/>
     </row>
-    <row r="262" ht="45" customHeight="1">
+    <row r="262" ht="150" customHeight="1">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
@@ -15138,27 +15130,31 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
       <c r="I262" s="5" t="inlineStr"/>
-      <c r="J262" s="5" t="inlineStr"/>
+      <c r="J262" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K262" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15166,23 +15162,27 @@
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N262" s="8" t="inlineStr"/>
-    </row>
-    <row r="263" ht="45" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N262" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="105" customHeight="1">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
@@ -15192,22 +15192,22 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N263" s="8" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15251,17 +15251,17 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15467,17 +15467,17 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15521,17 +15521,17 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15575,17 +15575,17 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15683,17 +15683,17 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
@@ -15770,13 +15770,13 @@
       </c>
       <c r="N273" s="8" t="inlineStr"/>
     </row>
-    <row r="274" ht="60" customHeight="1">
+    <row r="274" ht="45" customHeight="1">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15786,22 +15786,22 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -15814,23 +15814,23 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N274" s="8" t="inlineStr"/>
     </row>
-    <row r="275" ht="120" customHeight="1">
+    <row r="275" ht="45" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15840,39 +15840,27 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H275" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I275" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J275" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr"/>
+      <c r="I275" s="5" t="inlineStr"/>
+      <c r="J275" s="5" t="inlineStr"/>
       <c r="K275" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15880,27 +15868,23 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N275" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="75" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N275" s="8" t="inlineStr"/>
+    </row>
+    <row r="276" ht="60" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15910,22 +15894,22 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -15938,23 +15922,23 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
+          <t>cf702f2b4</t>
         </is>
       </c>
       <c r="N276" s="8" t="inlineStr"/>
     </row>
-    <row r="277" ht="60" customHeight="1">
+    <row r="277" ht="120" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15964,27 +15948,39 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
-        </is>
-      </c>
-      <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="5" t="inlineStr"/>
-      <c r="J277" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I277" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J277" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K277" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15992,23 +15988,27 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
-        </is>
-      </c>
-      <c r="N277" s="8" t="inlineStr"/>
-    </row>
-    <row r="278" ht="45" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N277" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="75" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -16018,22 +16018,22 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -16046,12 +16046,12 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N278" s="8" t="inlineStr"/>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -16077,17 +16077,17 @@
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16131,17 +16131,17 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -16159,18 +16159,18 @@
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N280" s="8" t="inlineStr"/>
     </row>
-    <row r="281" ht="45" customHeight="1">
+    <row r="281" ht="60" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16185,17 +16185,17 @@
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
@@ -16213,18 +16213,18 @@
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N281" s="8" t="inlineStr"/>
     </row>
-    <row r="282" ht="120" customHeight="1">
+    <row r="282" ht="45" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16234,22 +16234,22 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
@@ -16262,23 +16262,23 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N282" s="8" t="inlineStr"/>
     </row>
-    <row r="283" ht="60" customHeight="1">
+    <row r="283" ht="45" customHeight="1">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>TE-SESSION-CACHE</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16288,22 +16288,22 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Structural Targets</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>Session-date cache invalidation</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr"/>
@@ -16316,23 +16316,23 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>33146be5e</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N283" s="8" t="inlineStr"/>
     </row>
-    <row r="284" ht="60" customHeight="1">
+    <row r="284" ht="120" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16342,22 +16342,22 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
@@ -16370,23 +16370,23 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>93ec11842</t>
         </is>
       </c>
       <c r="N284" s="8" t="inlineStr"/>
     </row>
-    <row r="285" ht="105" customHeight="1">
+    <row r="285" ht="60" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-SESSION-CACHE</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16396,31 +16396,27 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Structural Targets</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>Session-date cache invalidation</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr"/>
       <c r="I285" s="5" t="inlineStr"/>
-      <c r="J285" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J285" s="5" t="inlineStr"/>
       <c r="K285" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16428,27 +16424,23 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N285" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="135" customHeight="1">
+          <t>33146be5e</t>
+        </is>
+      </c>
+      <c r="N285" s="8" t="inlineStr"/>
+    </row>
+    <row r="286" ht="60" customHeight="1">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16458,39 +16450,27 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H286" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I286" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
-      <c r="J286" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
-        </is>
-      </c>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="5" t="inlineStr"/>
+      <c r="J286" s="5" t="inlineStr"/>
       <c r="K286" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16498,27 +16478,23 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
-        </is>
-      </c>
-      <c r="N286" s="8" t="inlineStr">
-        <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="287" ht="45" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N286" s="8" t="inlineStr"/>
+    </row>
+    <row r="287" ht="105" customHeight="1">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C287" s="10" t="inlineStr">
@@ -16528,27 +16504,31 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr"/>
       <c r="I287" s="5" t="inlineStr"/>
-      <c r="J287" s="5" t="inlineStr"/>
+      <c r="J287" s="5" t="inlineStr">
+        <is>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+        </is>
+      </c>
       <c r="K287" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16556,23 +16536,27 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N287" s="8" t="inlineStr"/>
-    </row>
-    <row r="288" ht="120" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N287" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="135" customHeight="1">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C288" s="10" t="inlineStr">
@@ -16582,29 +16566,37 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
-        </is>
-      </c>
-      <c r="H288" s="2" t="inlineStr"/>
-      <c r="I288" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I288" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
         </is>
       </c>
       <c r="K288" s="12" t="inlineStr">
@@ -16614,27 +16606,27 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>42c36ef91</t>
         </is>
       </c>
       <c r="N288" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="60" customHeight="1">
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="45" customHeight="1">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C289" s="10" t="inlineStr">
@@ -16644,22 +16636,22 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr"/>
@@ -16672,23 +16664,23 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>50cace567</t>
         </is>
       </c>
       <c r="N289" s="8" t="inlineStr"/>
     </row>
-    <row r="290" ht="60" customHeight="1">
+    <row r="290" ht="120" customHeight="1">
       <c r="A290" s="2" t="n">
         <v>289</v>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C290" s="10" t="inlineStr">
@@ -16698,27 +16690,31 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr"/>
       <c r="I290" s="5" t="inlineStr"/>
-      <c r="J290" s="5" t="inlineStr"/>
+      <c r="J290" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K290" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16726,65 +16722,57 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
-        </is>
-      </c>
-      <c r="N290" s="8" t="inlineStr"/>
-    </row>
-    <row r="291" ht="45" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N290" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="60" customHeight="1">
       <c r="A291" s="2" t="n">
         <v>290</v>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C291" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>MOMENTUM-TAB</t>
+        </is>
+      </c>
+      <c r="C291" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H291" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I291" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J291" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr"/>
+      <c r="I291" s="5" t="inlineStr"/>
+      <c r="J291" s="5" t="inlineStr"/>
       <c r="K291" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16792,65 +16780,53 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M291" s="3" t="inlineStr"/>
-      <c r="N291" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="45" customHeight="1">
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N291" s="8" t="inlineStr"/>
+    </row>
+    <row r="292" ht="60" customHeight="1">
       <c r="A292" s="2" t="n">
         <v>291</v>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C292" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C292" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
-        </is>
-      </c>
-      <c r="H292" s="2" t="inlineStr">
-        <is>
-          <t>verified (no change needed)</t>
-        </is>
-      </c>
-      <c r="I292" s="5" t="inlineStr">
-        <is>
-          <t>Win: confirms infrastructure still healthy.</t>
-        </is>
-      </c>
-      <c r="J292" s="5" t="inlineStr">
-        <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="5" t="inlineStr"/>
+      <c r="J292" s="5" t="inlineStr"/>
       <c r="K292" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16858,15 +16834,15 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M292" s="3" t="inlineStr"/>
-      <c r="N292" s="8" t="inlineStr">
-        <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N292" s="8" t="inlineStr"/>
     </row>
     <row r="293" ht="45" customHeight="1">
       <c r="A293" s="2" t="n">
@@ -16874,7 +16850,7 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -16884,35 +16860,39 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J293" s="5" t="inlineStr"/>
+          <t>Win: persistence works; no silent overwrites.</t>
+        </is>
+      </c>
+      <c r="J293" s="5" t="inlineStr">
+        <is>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
       <c r="K293" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16920,17 +16900,13 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M293" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr"/>
       <c r="N293" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -16940,59 +16916,63 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C294" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C294" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K294" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L294" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K294" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M294" s="3" t="inlineStr"/>
       <c r="N294" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -17002,59 +16982,63 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
-        </is>
-      </c>
-      <c r="C295" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C295" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
-        </is>
-      </c>
-      <c r="J295" s="5" t="inlineStr">
-        <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K295" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L295" s="2" t="inlineStr"/>
-      <c r="M295" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J295" s="5" t="inlineStr"/>
+      <c r="K295" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N295" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -17064,257 +17048,381 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C296" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C296" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J296" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K296" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K296" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="3" t="inlineStr"/>
       <c r="N296" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="45" customHeight="1">
       <c r="A297" s="2" t="n">
         <v>296</v>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C297" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C297" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J297" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
-        </is>
-      </c>
-      <c r="K297" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L297" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K297" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr"/>
       <c r="M297" s="3" t="inlineStr"/>
       <c r="N297" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="195" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="45" customHeight="1">
       <c r="A298" s="2" t="n">
         <v>297</v>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E298" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I298" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J298" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K298" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr"/>
+      <c r="M298" s="3" t="inlineStr"/>
+      <c r="N298" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="75" customHeight="1">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C299" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E299" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I299" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J299" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K299" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M299" s="3" t="inlineStr"/>
+      <c r="N299" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="195" customHeight="1">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C298" s="10" t="inlineStr">
+      <c r="C300" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="D300" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E300" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
+      <c r="F300" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G298" s="5" t="inlineStr">
+      <c r="G300" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H298" s="2" t="inlineStr">
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I300" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J298" s="5" t="inlineStr">
+      <c r="J300" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K298" s="15" t="inlineStr">
+      <c r="K300" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L298" s="2" t="inlineStr">
+      <c r="L300" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="M298" s="3" t="inlineStr"/>
-      <c r="N298" s="8" t="inlineStr">
+      <c r="M300" s="3" t="inlineStr"/>
+      <c r="N300" s="8" t="inlineStr">
         <is>
           <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="90" customHeight="1">
-      <c r="A299" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="B299" s="3" t="inlineStr">
+    <row r="301" ht="90" customHeight="1">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C299" s="13" t="inlineStr">
+      <c r="C301" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D299" s="5" t="inlineStr">
+      <c r="D301" s="5" t="inlineStr">
         <is>
           <t>Data / Universe</t>
         </is>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E301" s="6" t="inlineStr">
         <is>
           <t>Russell 1000 historical membership (Sharadar SF1)</t>
         </is>
       </c>
-      <c r="F299" s="5" t="inlineStr">
+      <c r="F301" s="5" t="inlineStr">
         <is>
           <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
         </is>
       </c>
-      <c r="G299" s="5" t="inlineStr">
+      <c r="G301" s="5" t="inlineStr">
         <is>
           <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
         </is>
       </c>
-      <c r="H299" s="2" t="inlineStr">
+      <c r="H301" s="2" t="inlineStr">
         <is>
           <t>$$ + 1 day</t>
         </is>
       </c>
-      <c r="I299" s="5" t="inlineStr">
+      <c r="I301" s="5" t="inlineStr">
         <is>
           <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
         </is>
       </c>
-      <c r="J299" s="5" t="inlineStr">
+      <c r="J301" s="5" t="inlineStr">
         <is>
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K299" s="15" t="inlineStr">
+      <c r="K301" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L299" s="2" t="inlineStr">
+      <c r="L301" s="2" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="M299" s="3" t="inlineStr"/>
-      <c r="N299" s="8" t="inlineStr">
+      <c r="M301" s="3" t="inlineStr"/>
+      <c r="N301" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -17419,10 +17527,10 @@
         <v>86</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -17476,10 +17584,10 @@
         <v>111</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-15.xlsx
+++ b/cache/open_items_2026-06-15.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N301"/>
+  <dimension ref="A1:N302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7302,13 +7302,13 @@
       </c>
       <c r="N129" s="8" t="inlineStr"/>
     </row>
-    <row r="130" ht="60" customHeight="1">
+    <row r="130" ht="75" customHeight="1">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>AUTO-STOP-SIDE</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
@@ -7318,39 +7318,27 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Automation / Exits</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Wrong-sided protective stop on shorts</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>auto_engine.run_exits blindly submitted the stored plan stop; a long-style stop (entry-ATR) synced onto a short is a buy-stop below market -&gt; Alpaca rejects it ('stop price must be greater than current price'), leaving the short unprotected (NEM).</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>shipped (diagnosis); pending (fix)</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
-        </is>
-      </c>
-      <c r="J130" s="5" t="inlineStr">
-        <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
-        </is>
-      </c>
+          <t>Added _protective_stop() validating side vs live price (sell-stop below mkt for longs, buy-stop above for shorts); self-heals missing/wrong-sided stops to a side-correct fallback. Placed live NEM buy-stop $116.61; corrected stored portfolio_state stop 98.18-&gt;116.61.</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="5" t="inlineStr"/>
+      <c r="J130" s="5" t="inlineStr"/>
       <c r="K130" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7358,27 +7346,23 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
-        </is>
-      </c>
-      <c r="N130" s="8" t="inlineStr">
-        <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="105" customHeight="1">
+          <t>2e5dff9a0</t>
+        </is>
+      </c>
+      <c r="N130" s="8" t="inlineStr"/>
+    </row>
+    <row r="131" ht="60" customHeight="1">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
@@ -7388,37 +7372,37 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K131" s="12" t="inlineStr">
@@ -7428,27 +7412,27 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N131" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="45" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="105" customHeight="1">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7458,37 +7442,37 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K132" s="12" t="inlineStr">
@@ -7498,7 +7482,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M132" s="3" t="inlineStr">
@@ -7508,7 +7492,7 @@
       </c>
       <c r="N132" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7502,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
@@ -7533,22 +7517,22 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -7558,7 +7542,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K133" s="12" t="inlineStr">
@@ -7578,7 +7562,7 @@
       </c>
       <c r="N133" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7572,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
@@ -7603,32 +7587,32 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K134" s="12" t="inlineStr">
@@ -7648,17 +7632,17 @@
       </c>
       <c r="N134" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="60" customHeight="1">
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="45" customHeight="1">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -7673,32 +7657,32 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K135" s="12" t="inlineStr">
@@ -7718,17 +7702,17 @@
       </c>
       <c r="N135" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="105" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>BULLVEDA-FUNNEL-MARKETGATE</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
@@ -7738,27 +7722,39 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>BullVeda / Home</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Scan funnel paints whole universe bearish on market-gate days</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>On a market-wide entry-gate day (SPY -2.6% + 7 distribution days, 2026-06-08) the Home scan funnel showed 0 bullish / 0 neutral / 1000 avoid: realFunnel read decisions_by_mode (stamped AVOID on every gate-blocked name) and the universe tile read scan_count from the empty all_scored list. Engine was correct (no new longs on a crash day); the dashboard misrepresented it as universe-wide bearishness.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>realFunnel un-collapses entry-gate AVOIDs to the composite verdict + adds a 'no new longs today' banner (committed 57df99939/eb960bde8); build_data.py scan_count = len(all_scored)+len(killed); served data.critical.json scan_count patched 0-&gt;1000.</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr"/>
-      <c r="J136" s="5" t="inlineStr"/>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>1 hr</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Massive time savings</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+        </is>
+      </c>
       <c r="K136" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7766,23 +7762,27 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>eb960bde8</t>
-        </is>
-      </c>
-      <c r="N136" s="8" t="inlineStr"/>
-    </row>
-    <row r="137" ht="45" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N136" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="105" customHeight="1">
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>PEAD-7</t>
+          <t>BULLVEDA-FUNNEL-MARKETGATE</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
@@ -7792,22 +7792,22 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda / Home</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>PEAD data pipeline</t>
+          <t>Scan funnel paints whole universe bearish on market-gate days</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Wire EODHD past-earnings surprise + post-report gap</t>
+          <t>On a market-wide entry-gate day (SPY -2.6% + 7 distribution days, 2026-06-08) the Home scan funnel showed 0 bullish / 0 neutral / 1000 avoid: realFunnel read decisions_by_mode (stamped AVOID on every gate-blocked name) and the universe tile read scan_count from the empty all_scored list. Engine was correct (no new longs on a crash day); the dashboard misrepresented it as universe-wide bearishness.</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
+          <t>realFunnel un-collapses entry-gate AVOIDs to the composite verdict + adds a 'no new longs today' banner (committed 57df99939/eb960bde8); build_data.py scan_count = len(all_scored)+len(killed); served data.critical.json scan_count patched 0-&gt;1000.</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7820,23 +7820,23 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>f089b48ef</t>
+          <t>eb960bde8</t>
         </is>
       </c>
       <c r="N137" s="8" t="inlineStr"/>
     </row>
-    <row r="138" ht="60" customHeight="1">
+    <row r="138" ht="45" customHeight="1">
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PEAD-7</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
@@ -7846,39 +7846,27 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>PEAD data pipeline</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Wire EODHD past-earnings surprise + post-report gap</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>10 min after answer</t>
-        </is>
-      </c>
-      <c r="I138" s="5" t="inlineStr">
-        <is>
-          <t>Win: -158 lines + clearer docs.</t>
-        </is>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
-        </is>
-      </c>
+          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr"/>
+      <c r="J138" s="5" t="inlineStr"/>
       <c r="K138" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7886,27 +7874,23 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N138" s="8" t="inlineStr">
-        <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="90" customHeight="1">
+          <t>f089b48ef</t>
+        </is>
+      </c>
+      <c r="N138" s="8" t="inlineStr"/>
+    </row>
+    <row r="139" ht="60" customHeight="1">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
@@ -7921,32 +7905,32 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K139" s="12" t="inlineStr">
@@ -7966,17 +7950,17 @@
       </c>
       <c r="N139" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="75" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="90" customHeight="1">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>FUNNEL-BIAS-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
@@ -7986,27 +7970,39 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Scan funnel collapses on macro-gate days</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>BullVeda home SCAN FUNNEL classified direction by the macro-gated action verdict, not bias. On the 2026-06-11 CPI blackout day the top-level gate flattened every verdict to WAIT, so the funnel showed 1 bullish / 1074 neutral / 0 avoid when the real bias distribution was 263 bull / 456 neu / 189 bear.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>realFunnel now classifies by the per-mode bias axis (decisions_by_mode[key].bias -&gt; raw.bias -&gt; window.biasRead), gate-blind; gateBlocked overlay + extracted gateReason (top-level decision.reason) drives the 'No new longs today · Macro blackout: CPI — 719 entry-gated' banner. Rebuilt via build_bullveda.cjs.</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr"/>
-      <c r="J140" s="5" t="inlineStr"/>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>30 min after answers</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~3-5K lines if mostly stale.</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+        </is>
+      </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8014,15 +8010,19 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
-        </is>
-      </c>
-      <c r="N140" s="8" t="inlineStr"/>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N140" s="8" t="inlineStr">
+        <is>
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="75" customHeight="1">
       <c r="A141" s="2" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>FUNNEL-BIAS-2</t>
+          <t>FUNNEL-BIAS-1</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>Funnel click-through blanked the scanner</t>
+          <t>Scan funnel collapses on macro-gate days</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Clicking the SCAN FUNNEL 'bullish' stat passed scan('BUY') which filtered the scanner by t.verdict==='BUY'. After FUNNEL-BIAS-1 the funnel counts by bias (263) but the scanner still filtered by the macro-gated verdict (1 BUY on CPI day) -&gt; scanner showed blank.</t>
+          <t>BullVeda home SCAN FUNNEL classified direction by the macro-gated action verdict, not bias. On the 2026-06-11 CPI blackout day the top-level gate flattened every verdict to WAIT, so the funnel showed 1 bullish / 1074 neutral / 0 avoid when the real bias distribution was 263 bull / 456 neu / 189 bear.</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>Added per-mode biasByMode to the scanRows row (boot.js from decisions_by_mode[k].bias); scanner 'Directional bias' side toggle now filters by per-mode bias (window.__tmode) with t.bias-&gt;verdict fallback. Funnel and scanner now show identical per-mode counts (swing 263/456/189). Rebuilt.</t>
+          <t>realFunnel now classifies by the per-mode bias axis (decisions_by_mode[key].bias -&gt; raw.bias -&gt; window.biasRead), gate-blind; gateBlocked overlay + extracted gateReason (top-level decision.reason) drives the 'No new longs today · Macro blackout: CPI — 719 entry-gated' banner. Rebuilt via build_bullveda.cjs.</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr"/>
@@ -8078,13 +8078,13 @@
       </c>
       <c r="N141" s="8" t="inlineStr"/>
     </row>
-    <row r="142" ht="90" customHeight="1">
+    <row r="142" ht="75" customHeight="1">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>FUNNEL-BIAS-3</t>
+          <t>FUNNEL-BIAS-2</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
@@ -8099,17 +8099,17 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Scanner frozen to page-load snapshot</t>
+          <t>Funnel click-through blanked the scanner</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>surface-signal SS_UNIVERSE is a module-level const evaluated once at page-load; the rows memo read it directly. The home SCAN FUNNEL reads scanRows() live every render, so after any data auto-refresh (5-min poll) or a new scan landing, funnel and scanner drifted apart — funnel 336 (live per-mode bullish) vs scanner 233 (older frozen snapshot).</t>
+          <t>Clicking the SCAN FUNNEL 'bullish' stat passed scan('BUY') which filtered the scanner by t.verdict==='BUY'. After FUNNEL-BIAS-1 the funnel counts by bias (263) but the scanner still filtered by the macro-gated verdict (1 BUY on CPI day) -&gt; scanner showed blank.</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>rows memo now reads window.__BV.scanRows() live (with SS_UNIVERSE mock fallback offline) instead of the frozen const, so the scanner always reflects the same snapshot the funnel does. Rebuilt.</t>
+          <t>Added per-mode biasByMode to the scanRows row (boot.js from decisions_by_mode[k].bias); scanner 'Directional bias' side toggle now filters by per-mode bias (window.__tmode) with t.bias-&gt;verdict fallback. Funnel and scanner now show identical per-mode counts (swing 263/456/189). Rebuilt.</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr"/>
@@ -8132,13 +8132,13 @@
       </c>
       <c r="N142" s="8" t="inlineStr"/>
     </row>
-    <row r="143" ht="105" customHeight="1">
+    <row r="143" ht="90" customHeight="1">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-FILTER-AUDIT-1</t>
+          <t>FUNNEL-BIAS-3</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
@@ -8153,17 +8153,17 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>Scanner filter audit — 6 bugs</t>
+          <t>Scanner frozen to page-load snapshot</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Full audit of scanner tabs+pills+side+columns. Bugs: (1) INSIDER pill filtered t.sent NEWS sentiment not insider data; (2) INSIDER signal flag filtered empty insUsd; (3) EXCLUDED tab used gated verdict==AVOID → 0 on macro-gate days; (4) FRESH tab was a slice(0,3) placeholder; (5) TOP 20% SCORE pill used absolute score&gt;=70 (top ~12pct) not a real percentile; (6) tab badge counts frozen to module-const SS_UNIVERSE (EARNINGS 161 vs live 36).</t>
+          <t>surface-signal SS_UNIVERSE is a module-level const evaluated once at page-load; the rows memo read it directly. The home SCAN FUNNEL reads scanRows() live every render, so after any data auto-refresh (5-min poll) or a new scan landing, funnel and scanner drifted apart — funnel 336 (live per-mode bullish) vs scanner 233 (older frozen snapshot).</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>INSIDER pill+signal -&gt; insider_net&gt;0; EXCLUDED -&gt; bias bearish (matches funnel, 224); FRESH -&gt; entry_quality==FRESH (125); TOP20 -&gt; true 80th-pctile (score&gt;=63, 220); tab counts recomputed live from scanRows. Rebuilt. Noted feed-limited: insider_usd empty, ai-edge p_up sparse, breakout pill = family-match incl coiled.</t>
+          <t>rows memo now reads window.__BV.scanRows() live (with SS_UNIVERSE mock fallback offline) instead of the frozen const, so the scanner always reflects the same snapshot the funnel does. Rebuilt.</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr"/>
@@ -8181,18 +8181,18 @@
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N143" s="8" t="inlineStr"/>
     </row>
-    <row r="144" ht="60" customHeight="1">
+    <row r="144" ht="105" customHeight="1">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>EODHD-RATE-FIX</t>
+          <t>SCANNER-FILTER-AUDIT-1</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
@@ -8202,22 +8202,22 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Data / EODHD (rate-limit)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Per-minute rate-limit fix — enrichment burst</t>
+          <t>Scanner filter audit — 6 bugs</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>max_enrichment_tickers regressed 3000 (was 300/700); deep-enriched ~2500 tickers x ~14 endpoints, bursting EODHD 950/min. Reverted to validated 700. Bulk endpoint + dedup were ALREADY done (brief diagnosis was wrong).</t>
+          <t>Full audit of scanner tabs+pills+side+columns. Bugs: (1) INSIDER pill filtered t.sent NEWS sentiment not insider data; (2) INSIDER signal flag filtered empty insUsd; (3) EXCLUDED tab used gated verdict==AVOID → 0 on macro-gate days; (4) FRESH tab was a slice(0,3) placeholder; (5) TOP 20% SCORE pill used absolute score&gt;=70 (top ~12pct) not a real percentile; (6) tab badge counts frozen to module-const SS_UNIVERSE (EARNINGS 161 vs live 36).</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>config max_enrichment_tickers + job-restructure (cross-process limiter)</t>
+          <t>INSIDER pill+signal -&gt; insider_net&gt;0; EXCLUDED -&gt; bias bearish (matches funnel, 224); FRESH -&gt; entry_quality==FRESH (125); TOP20 -&gt; true 80th-pctile (score&gt;=63, 220); tab counts recomputed live from scanRows. Rebuilt. Noted feed-limited: insider_usd empty, ai-edge p_up sparse, breakout pill = family-match incl coiled.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
@@ -8230,12 +8230,12 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>0a346032b</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N144" s="8" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>DATA-WIRE-NO-DEMO</t>
+          <t>EODHD-RATE-FIX</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
@@ -8256,22 +8256,22 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Data Wiring</t>
+          <t>Data / EODHD (rate-limit)</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>Kill fabrications + wire real fields (no demo data)</t>
+          <t>Per-minute rate-limit fix — enrichment burst</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>removed AI-chart synthetic candles + DCF synthetic base; wired p_up (ml_edge), revision breadth (earnings_beat), Schwab option Greeks, DCF net-debt, beta, crowding — fallback-safe</t>
+          <t>max_enrichment_tickers regressed 3000 (was 300/700); deep-enriched ~2500 tickers x ~14 endpoints, bursting EODHD 950/min. Reverted to validated 700. Bulk endpoint + dedup were ALREADY done (brief diagnosis was wrong).</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html + server.py /api/ticker,/api/universe,/api/options</t>
+          <t>config max_enrichment_tickers + job-restructure (cross-process limiter)</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
@@ -8289,18 +8289,18 @@
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>1a9103f67</t>
+          <t>0a346032b</t>
         </is>
       </c>
       <c r="N145" s="8" t="inlineStr"/>
     </row>
-    <row r="146" ht="75" customHeight="1">
+    <row r="146" ht="60" customHeight="1">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>CONGRESS-FLOW-1</t>
+          <t>DATA-WIRE-NO-DEMO</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
@@ -8310,22 +8310,22 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Data · Smart Money</t>
+          <t>Data Wiring</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Congressional / political-flow tracker</t>
+          <t>Kill fabrications + wire real fields (no demo data)</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>Reconnect dead congress feeds (Senate/House Stock Watcher 403, Capitol Trades 429) via multi-source cascade; surface as Congress board + per-ticker Intel tile + Home strip, joined to our verdict</t>
+          <t>removed AI-chart synthetic candles + DCF synthetic base; wired p_up (ml_edge), revision breadth (earnings_beat), Schwab option Greeks, DCF net-debt, beta, crowding — fallback-safe</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>congress_trades.py (Quiver beta + Capitol + House Clerk + Senate eFD, preserve-on-degrade) -&gt; cache/congressional_picks.json -&gt; /api/congress[/{ticker}] -&gt; SurfaceCongress + surface-signal Sec10 + CongressBuyingStrip; nightly scripts/refresh_congress.py + launchd congress-refresh.plist</t>
+          <t>Stocksmith.html + server.py /api/ticker,/api/universe,/api/options</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
@@ -8338,23 +8338,23 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>1bc69ae57</t>
+          <t>1a9103f67</t>
         </is>
       </c>
       <c r="N146" s="8" t="inlineStr"/>
     </row>
-    <row r="147" ht="90" customHeight="1">
+    <row r="147" ht="75" customHeight="1">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>EODHD-SHARED-LIMITER</t>
+          <t>CONGRESS-FLOW-1</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
@@ -8364,22 +8364,22 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Data/EODHD</t>
+          <t>Data · Smart Money</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>Scale daily scan to top 1500 + NASDAQ without aborts</t>
+          <t>Congressional / political-flow tracker</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Per-process EODHD limiter let concurrent jobs burst past 1000/min -&gt; 429s -&gt; 31% fill -&gt; 30% abort guard, silently capping the scan at ~744. Also deep_enrichment_top_n==max_enrichment so deep runs scraped WSB/StockTwits/congressional on all names and stalled.</t>
+          <t>Reconnect dead congress feeds (Senate/House Stock Watcher 403, Capitol Trades 429) via multi-source cascade; surface as Congress board + per-ticker Intel tile + Home strip, joined to our verdict</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Added cross-process _SharedRateLimiter (flock-backed, one 950/min budget for the whole key, fail-open); raised max_enrichment_tickers 1000-&gt;1500; decoupled deep_enrichment_top_n 1500-&gt;500 so only top 500 get heavy scrapes while 1500 still score. include_nasdaq_all + full-mode already on. Validated: universe 3622 incl NDXall=1000, 91% fill no abort, 1500 scored (1004 passed + 496 killed).</t>
+          <t>congress_trades.py (Quiver beta + Capitol + House Clerk + Senate eFD, preserve-on-degrade) -&gt; cache/congressional_picks.json -&gt; /api/congress[/{ticker}] -&gt; SurfaceCongress + surface-signal Sec10 + CongressBuyingStrip; nightly scripts/refresh_congress.py + launchd congress-refresh.plist</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
@@ -8392,23 +8392,23 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>fabb3562f</t>
+          <t>1bc69ae57</t>
         </is>
       </c>
       <c r="N147" s="8" t="inlineStr"/>
     </row>
-    <row r="148" ht="75" customHeight="1">
+    <row r="148" ht="90" customHeight="1">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>MODE-1</t>
+          <t>EODHD-SHARED-LIMITER</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
@@ -8418,22 +8418,22 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data/EODHD</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Per-mode SWING/POSITION/INVEST decisions (Option A · Phase 1)</t>
+          <t>Scale daily scan to top 1500 + NASDAQ without aborts</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>UI mode toggle was cosmetic — t.decision and t.canonical_trade_plan were strategy-agnostic single fields. Toggling SWING/POS/INV in detail header did not change verdict, stop, T1/T2, or R:R. Users with informed conviction couldn't get a mode-specific read.</t>
+          <t>Per-process EODHD limiter let concurrent jobs burst past 1000/min -&gt; 429s -&gt; 31% fill -&gt; 30% abort guard, silently capping the scan at ~744. Also deep_enrichment_top_n==max_enrichment so deep runs scraped WSB/StockTwits/congressional on all names and stalled.</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>New _MODE_RULEBOOK + compute_decisions_by_mode() in analysis.py. Each mode applies own stop (1.25/1.75x ATR or -15% DD), R:R floor (3.0/2.5/2.0), entry-quality gate, earnings blackout. Output as t.decisions_by_mode={swing,position,investment}. Frontend reads via _qdStrategyCurrent().</t>
+          <t>Added cross-process _SharedRateLimiter (flock-backed, one 950/min budget for the whole key, fail-open); raised max_enrichment_tickers 1000-&gt;1500; decoupled deep_enrichment_top_n 1500-&gt;500 so only top 500 get heavy scrapes while 1500 still score. include_nasdaq_all + full-mode already on. Validated: universe 3622 incl NDXall=1000, 91% fill no abort, 1500 scored (1004 passed + 496 killed).</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>3e812743</t>
+          <t>fabb3562f</t>
         </is>
       </c>
       <c r="N148" s="8" t="inlineStr"/>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>MODE-2</t>
+          <t>MODE-1</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
@@ -8477,17 +8477,17 @@
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>Per-mode sizing + verdict-divergence explanation (Phase 2)</t>
+          <t>Per-mode SWING/POSITION/INVEST decisions (Option A · Phase 1)</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>Per-mode decisions shipped in MODE-1 didn't apply mode-specific size_mult or explain WHY a mode's verdict differed from the legacy single-decision.</t>
+          <t>UI mode toggle was cosmetic — t.decision and t.canonical_trade_plan were strategy-agnostic single fields. Toggling SWING/POS/INV in detail header did not change verdict, stop, T1/T2, or R:R. Users with informed conviction couldn't get a mode-specific read.</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>compute_decisions_by_mode() now accepts base_alloc_pct + legacy_decision. Per-mode final_alloc_pct = base × size_mult, capped 5% NAV. New diverge_note field surfaces the exact rule that caused divergence (R:R floor, entry-quality gate, ER blackout). Frontend chip shows size + amber divergence pill.</t>
+          <t>New _MODE_RULEBOOK + compute_decisions_by_mode() in analysis.py. Each mode applies own stop (1.25/1.75x ATR or -15% DD), R:R floor (3.0/2.5/2.0), entry-quality gate, earnings blackout. Output as t.decisions_by_mode={swing,position,investment}. Frontend reads via _qdStrategyCurrent().</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
@@ -8505,18 +8505,18 @@
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>d5eb49c5</t>
+          <t>3e812743</t>
         </is>
       </c>
       <c r="N149" s="8" t="inlineStr"/>
     </row>
-    <row r="150" ht="105" customHeight="1">
+    <row r="150" ht="75" customHeight="1">
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>MODE-3</t>
+          <t>MODE-2</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>Per-mode pillar reweighting (Phase 3 · flag-gated · INTUITION pending validation)</t>
+          <t>Per-mode sizing + verdict-divergence explanation (Phase 2)</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Per-mode rulebooks shipped in MODE-1+2 used the legacy single composite score. SWING couldn't naturally select catalyst-heavy setups vs INVEST selecting fundamentals-heavy. User explicitly overrode principle-7 evidence requirement to ship the per-mode UX immediately.</t>
+          <t>Per-mode decisions shipped in MODE-1 didn't apply mode-specific size_mult or explain WHY a mode's verdict differed from the legacy single-decision.</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>New _MODE_PILLAR_WEIGHTS in analysis.py (SWING catalyst+tech-heavy, POS balanced, INVEST fund-heavy). compute_decisions_by_mode accepts pillar_pcts and computes mode_score = sum(pct × weight × 100). Config flag per_mode_pillar_reweight._enabled (default true) for rollback. Legacy t.score still drives decision_log + alerts; per-mode score affects UI only. Chip shows 'score 58 (legacy 45)' when divergence ≥5pts. Validation backtest required before promoting (see MODE-4).</t>
+          <t>compute_decisions_by_mode() now accepts base_alloc_pct + legacy_decision. Per-mode final_alloc_pct = base × size_mult, capped 5% NAV. New diverge_note field surfaces the exact rule that caused divergence (R:R floor, entry-quality gate, ER blackout). Frontend chip shows size + amber divergence pill.</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
@@ -8559,18 +8559,18 @@
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>6df0095d</t>
+          <t>d5eb49c5</t>
         </is>
       </c>
       <c r="N150" s="8" t="inlineStr"/>
     </row>
-    <row r="151" ht="90" customHeight="1">
+    <row r="151" ht="105" customHeight="1">
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>VERDICT-TWO-AXIS</t>
+          <t>MODE-3</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
@@ -8585,17 +8585,17 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>Two-axis verdict (bias × action × reason_class) replaces overloaded enum</t>
+          <t>Per-mode pillar reweighting (Phase 3 · flag-gated · INTUITION pending validation)</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>Single verdict enum conflated DIRECTION and ACTION — an AVOID-by-extended-gate long (WKC, strong uptrend) rendered 'Bearish · Place short'. Engine now emits orthogonal bias (bullish/neutral/bearish) + action (buy/wait/avoid/short) + reason_class; surfaces bind bias for the word, action for the chip, reason for the caveat.</t>
+          <t>Per-mode rulebooks shipped in MODE-1+2 used the legacy single composite score. SWING couldn't naturally select catalyst-heavy setups vs INVEST selecting fundamentals-heavy. User explicitly overrode principle-7 evidence requirement to ship the per-mode UX immediately.</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>decision_engine.derive_bias_action + compute_final_verdict wrapper; analysis.compute_decisions_by_mode per-mode; server /api/universe exposes; bullveda-boot maps; data.jsx biasRead/actionRead/reasonNote; migrated composite-verdict + scan-column + detail-panel + lens-investment + lens-overview + surface-signal + surface-watchlist + home. Verdict enum kept for back-compat.</t>
+          <t>New _MODE_PILLAR_WEIGHTS in analysis.py (SWING catalyst+tech-heavy, POS balanced, INVEST fund-heavy). compute_decisions_by_mode accepts pillar_pcts and computes mode_score = sum(pct × weight × 100). Config flag per_mode_pillar_reweight._enabled (default true) for rollback. Legacy t.score still drives decision_log + alerts; per-mode score affects UI only. Chip shows 'score 58 (legacy 45)' when divergence ≥5pts. Validation backtest required before promoting (see MODE-4).</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
@@ -8608,12 +8608,12 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>3b6c90547</t>
+          <t>6df0095d</t>
         </is>
       </c>
       <c r="N151" s="8" t="inlineStr"/>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>UI-AGENCY-1</t>
+          <t>VERDICT-TWO-AXIS</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
@@ -8634,22 +8634,22 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Detail Page UX</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Always-visible BUY/SHORT/WATCH action bar (user agency)</t>
+          <t>Two-axis verdict (bias × action × reason_class) replaces overloaded enum</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>Detail page hid the BUY ribbon when system verdict was WATCH/AVOID/EXTENDED. A trader with informed conviction couldn't act through the dashboard. User explicit direction: system informs, user decides.</t>
+          <t>Single verdict enum conflated DIRECTION and ACTION — an AVOID-by-extended-gate long (WKC, strong uptrend) rendered 'Bearish · Place short'. Engine now emits orthogonal bias (bullish/neutral/bearish) + action (buy/wait/avoid/short) + reason_class; surfaces bind bias for the word, action for the chip, reason for the caveat.</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>New renderQuickActionBar (sticky detail-header) + window._openQuickAction(action, ticker, ctx) global router. System verdict shown as informational chip only; buttons never gated on score/R:R/PLAN INCOMPLETE. WATCH POSTs to /api/custom/add with idempotent 'already tracked' handling. Memory: feedback_user_agency_actions.md.</t>
+          <t>decision_engine.derive_bias_action + compute_final_verdict wrapper; analysis.compute_decisions_by_mode per-mode; server /api/universe exposes; bullveda-boot maps; data.jsx biasRead/actionRead/reasonNote; migrated composite-verdict + scan-column + detail-panel + lens-investment + lens-overview + surface-signal + surface-watchlist + home. Verdict enum kept for back-compat.</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
@@ -8662,23 +8662,23 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>c97db4b4</t>
+          <t>3b6c90547</t>
         </is>
       </c>
       <c r="N152" s="8" t="inlineStr"/>
     </row>
-    <row r="153" ht="60" customHeight="1">
+    <row r="153" ht="90" customHeight="1">
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>SCORE-ZERO-LABEL</t>
+          <t>UI-AGENCY-1</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
@@ -8688,22 +8688,22 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Composite Score</t>
+          <t>Detail Page UX</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>Score=0 generic SUB-THRESHOLD masked the actual kill cause</t>
+          <t>Always-visible BUY/SHORT/WATCH action bar (user agency)</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Composite Score gauge always said 'SUB-THRESHOLD · −65 to BUY' for score=0. Now distinguishes PORTFOLIO BRAKE (system-wide pause) vs HARD GATE (per-ticker kill) vs SUPPRESSED vs genuinely SUB-THRESHOLD based on t.decision.reason</t>
+          <t>Detail page hid the BUY ribbon when system verdict was WATCH/AVOID/EXTENDED. A trader with informed conviction couldn't act through the dashboard. User explicit direction: system informs, user decides.</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>kairos.html — _scoreTierTxt + _scoreDeltaTxt computation rewritten with reason-aware branching</t>
+          <t>New renderQuickActionBar (sticky detail-header) + window._openQuickAction(action, ticker, ctx) global router. System verdict shown as informational chip only; buttons never gated on score/R:R/PLAN INCOMPLETE. WATCH POSTs to /api/custom/add with idempotent 'already tracked' handling. Memory: feedback_user_agency_actions.md.</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
@@ -8716,23 +8716,23 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>c97db4b4</t>
         </is>
       </c>
       <c r="N153" s="8" t="inlineStr"/>
     </row>
-    <row r="154" ht="75" customHeight="1">
+    <row r="154" ht="60" customHeight="1">
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>PREMORTEM-REASON</t>
+          <t>SCORE-ZERO-LABEL</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
@@ -8742,22 +8742,22 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Pre-Mortem</t>
+          <t>Detail UI / Composite Score</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>Pre-Mortem showed boilerplate instead of real kill reason</t>
+          <t>Score=0 generic SUB-THRESHOLD masked the actual kill cause</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>When a ticker is in bundle.killed (e.g., rolling-Sharpe brake or earnings blackout), Pre-Mortem was generating speculative killers from current signals instead of surfacing t.decision.reason. Now prepends real reason with severity tag (PORTFOLIO SAFETY BRAKE / HARD GATE FAIL / SYSTEM KILL)</t>
+          <t>Composite Score gauge always said 'SUB-THRESHOLD · −65 to BUY' for score=0. Now distinguishes PORTFOLIO BRAKE (system-wide pause) vs HARD GATE (per-ticker kill) vs SUPPRESSED vs genuinely SUB-THRESHOLD based on t.decision.reason</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>kairos.html _qdAutoThesisKillers() — block 0 reads dec.reason and ranks priority 200</t>
+          <t>kairos.html — _scoreTierTxt + _scoreDeltaTxt computation rewritten with reason-aware branching</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
@@ -8780,13 +8780,13 @@
       </c>
       <c r="N154" s="8" t="inlineStr"/>
     </row>
-    <row r="155" ht="60" customHeight="1">
+    <row r="155" ht="75" customHeight="1">
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ELITE-STRUCT-TARGETS</t>
+          <t>PREMORTEM-REASON</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
@@ -8796,22 +8796,22 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Elite Picks</t>
+          <t>Detail UI / Pre-Mortem</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>Position/Invest cells bypassed structural targets</t>
+          <t>Pre-Mortem showed boilerplate instead of real kill reason</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Elite read precomputed bundle whose Position/Invest t1/t2 were clobbered by ATR/% math (build_data _mode_plan), so 6/9 elite cells + all shorts showed legacy targets that the overhead_supply_gate never touched — inconsistent with Overview</t>
+          <t>When a ticker is in bundle.killed (e.g., rolling-Sharpe brake or earnings blackout), Pre-Mortem was generating speculative killers from current signals instead of surfacing t.decision.reason. Now prepends real reason with severity tag (PORTFOLIO SAFETY BRAKE / HARD GATE FAIL / SYSTEM KILL)</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>build_data _mode_plan now prefers structural ladder from target_engine cache (cache-only read, 12h fresh+schema gated, no live fetch); keeps mode-appropriate stop; falls back to ATR/% on cold cache</t>
+          <t>kairos.html _qdAutoThesisKillers() — block 0 reads dec.reason and ranks priority 200</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
@@ -8824,23 +8824,23 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N155" s="8" t="inlineStr"/>
     </row>
-    <row r="156" ht="45" customHeight="1">
+    <row r="156" ht="60" customHeight="1">
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>ELITE-STRUCT-TARGETS</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
@@ -8850,39 +8850,27 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Elite Picks</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Position/Invest cells bypassed structural targets</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Elite read precomputed bundle whose Position/Invest t1/t2 were clobbered by ATR/% math (build_data _mode_plan), so 6/9 elite cells + all shorts showed legacy targets that the overhead_supply_gate never touched — inconsistent with Overview</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I156" s="5" t="inlineStr">
-        <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
-        </is>
-      </c>
-      <c r="J156" s="5" t="inlineStr">
-        <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
-        </is>
-      </c>
+          <t>build_data _mode_plan now prefers structural ladder from target_engine cache (cache-only read, 12h fresh+schema gated, no live fetch); keeps mode-appropriate stop; falls back to ATR/% on cold cache</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="5" t="inlineStr"/>
+      <c r="J156" s="5" t="inlineStr"/>
       <c r="K156" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8890,27 +8878,23 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N156" s="8" t="inlineStr">
-        <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="75" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N156" s="8" t="inlineStr"/>
+    </row>
+    <row r="157" ht="45" customHeight="1">
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>SUPA-SYNC-FK</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
@@ -8925,22 +8909,34 @@
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>supabase-sync chronic exit=1 (closed_trades FK + signal_log reset)</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>Every-30-min supabase-sync failed exit=1: closed_trades poisoned by an OCC option symbol (ARMK260717C00050000, 19 chars) excluded from the tickers FK upsert; signal_log abandoned ~2400 rows on a transient Connection-reset because the batch loop broke on first error with no retry.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>Added _norm_ticker (OCC option-&gt;underlying, e.g. ARMK) used by both the tickers and closed_trades builders so FK targets always exist; hardened _migrate_one with transient-error retry+backoff, removed the break (continue remaining batches), and added per-row fallback so one poison row can't drop its 100-row batch.</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="5" t="inlineStr"/>
-      <c r="J157" s="5" t="inlineStr"/>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+        </is>
+      </c>
       <c r="K157" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8948,23 +8944,27 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>f05c7c27c</t>
-        </is>
-      </c>
-      <c r="N157" s="8" t="inlineStr"/>
-    </row>
-    <row r="158" ht="60" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N157" s="8" t="inlineStr">
+        <is>
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="75" customHeight="1">
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>SUPA-SYNC-FK</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
@@ -8974,39 +8974,27 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>supabase-sync chronic exit=1 (closed_trades FK + signal_log reset)</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Every-30-min supabase-sync failed exit=1: closed_trades poisoned by an OCC option symbol (ARMK260717C00050000, 19 chars) excluded from the tickers FK upsert; signal_log abandoned ~2400 rows on a transient Connection-reset because the batch loop broke on first error with no retry.</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I158" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
-      <c r="J158" s="5" t="inlineStr">
-        <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
-        </is>
-      </c>
+          <t>Added _norm_ticker (OCC option-&gt;underlying, e.g. ARMK) used by both the tickers and closed_trades builders so FK targets always exist; hardened _migrate_one with transient-error retry+backoff, removed the break (continue remaining batches), and added per-row fallback so one poison row can't drop its 100-row batch.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="5" t="inlineStr"/>
+      <c r="J158" s="5" t="inlineStr"/>
       <c r="K158" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9014,27 +9002,23 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N158" s="8" t="inlineStr">
-        <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="75" customHeight="1">
+          <t>f05c7c27c</t>
+        </is>
+      </c>
+      <c r="N158" s="8" t="inlineStr"/>
+    </row>
+    <row r="159" ht="60" customHeight="1">
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>SCAN-CONN-BREAKER</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -9044,27 +9028,39 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Scan resilience</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>EODHD connectivity circuit breaker + nightly fd bump</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>Heavy scan with no fd-limit raise exhausted launchd's ~256 fds 21min in (2026-06-04 05:15 run); getaddrinfo failures then ground for 90min with zero progress before external kill, froze the BullVeda bundle + blocked later scans</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>Added EODHDConnectivityError breaker in eodhd_client._request: trips after 40 consecutive connection-establishment failures, fails all calls fast (no socket/retry), resets on any HTTP response; raised weekly_full_enrich.sh fd limit 10240→200000 to match run_daily_scan.sh</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="5" t="inlineStr"/>
-      <c r="J159" s="5" t="inlineStr"/>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+        </is>
+      </c>
       <c r="K159" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9072,23 +9068,27 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>71b02de8d</t>
-        </is>
-      </c>
-      <c r="N159" s="8" t="inlineStr"/>
-    </row>
-    <row r="160" ht="45" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N159" s="8" t="inlineStr">
+        <is>
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="75" customHeight="1">
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>FINBERT-SENTIMENT</t>
+          <t>SCAN-CONN-BREAKER</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
@@ -9098,22 +9098,22 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>ML / Features</t>
+          <t>Infrastructure / Scan resilience</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>FinBERT ONNX sentiment replaces keyword lexicon</t>
+          <t>EODHD connectivity circuit breaker + nightly fd bump</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>local ONNX FinBERT (no torch/LLM) primary scorer in get_news_sentiment, lexicon fallback; live pillar upgrade now; GBM-feature later via leak-free fwd log</t>
+          <t>Heavy scan with no fd-limit raise exhausted launchd's ~256 fds 21min in (2026-06-04 05:15 run); getaddrinfo failures then ground for 90min with zero progress before external kill, froze the BullVeda bundle + blocked later scans</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>finbert_sentiment.py + download_finbert_onnx.py + data_fetcher</t>
+          <t>Added EODHDConnectivityError breaker in eodhd_client._request: trips after 40 consecutive connection-establishment failures, fails all calls fast (no socket/retry), resets on any HTTP response; raised weekly_full_enrich.sh fd limit 10240→200000 to match run_daily_scan.sh</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
@@ -9126,23 +9126,23 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>7f1e2a9c4</t>
+          <t>71b02de8d</t>
         </is>
       </c>
       <c r="N160" s="8" t="inlineStr"/>
     </row>
-    <row r="161" ht="105" customHeight="1">
+    <row r="161" ht="45" customHeight="1">
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-CORE</t>
+          <t>FINBERT-SENTIMENT</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
@@ -9152,22 +9152,22 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / AI Prediction</t>
+          <t>ML / Features</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>Workspace AI Prediction sub-tab (23 modules)</t>
+          <t>FinBERT ONNX sentiment replaces keyword lexicon</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>Universe-wide forecasting workbench: hero cone · trade-exec strip · live-quote chip · stability badge · stress overlay · landmines · walk-forward equity · cross-horizon coherence · forward distribution histogram · calibration + reliability · universe scans (Top 10 Bulls/Bears/Flip/R:R + SHAP-per-row) · sector rollup · pair trades · open positions overlay · diff vs yesterday · R2000 alpha leak · drift trend · failure log</t>
+          <t>local ONNX FinBERT (no torch/LLM) primary scorer in get_news_sentiment, lexicon fallback; live pillar upgrade now; GBM-feature later via leak-free fwd log</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>kairos.html _qdMlAiBody + 23 sub-modules · shared between Workspaces ML Edge tab and QuantDetail per-ticker view via window._qdMlAiBody</t>
+          <t>finbert_sentiment.py + download_finbert_onnx.py + data_fetcher</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
@@ -9180,23 +9180,23 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>7f1e2a9c4</t>
         </is>
       </c>
       <c r="N161" s="8" t="inlineStr"/>
     </row>
-    <row r="162" ht="60" customHeight="1">
+    <row r="162" ht="105" customHeight="1">
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-AUTOREFRESH</t>
+          <t>AIPRED-CORE</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
@@ -9206,22 +9206,22 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Autonomous</t>
+          <t>ML Edge / AI Prediction</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Autonomous launchd jobs (full + intraday refresh)</t>
+          <t>Workspace AI Prediction sub-tab (23 modules)</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>5 AM PT full universe + 9/11/13 PT intraday top-100. Loaded + tested 2026-05-18. Output: cache/ml_edge_predictions.json + infra/prototype/ ml_edge_predictions.json</t>
+          <t>Universe-wide forecasting workbench: hero cone · trade-exec strip · live-quote chip · stability badge · stress overlay · landmines · walk-forward equity · cross-horizon coherence · forward distribution histogram · calibration + reliability · universe scans (Top 10 Bulls/Bears/Flip/R:R + SHAP-per-row) · sector rollup · pair trades · open positions overlay · diff vs yesterday · R2000 alpha leak · drift trend · failure log</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.ml-edge.plist + .ml-edge-intraday.plist (installed at ~/Library/LaunchAgents/)</t>
+          <t>kairos.html _qdMlAiBody + 23 sub-modules · shared between Workspaces ML Edge tab and QuantDetail per-ticker view via window._qdMlAiBody</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-SCHWAB</t>
+          <t>AIPRED-AUTOREFRESH</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
@@ -9260,22 +9260,22 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Real Quotes</t>
+          <t>ML Edge / Autonomous</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>Real Schwab bid/ask spread overlay (top-100)</t>
+          <t>Autonomous launchd jobs (full + intraday refresh)</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>Batch-fetches live Schwab quotes for top-100 picks per mode; overrides ADV-band heuristic with real spread_bps; q50_net recomputed; spread_source='schwab_live' stamped</t>
+          <t>5 AM PT full universe + 9/11/13 PT intraday top-100. Loaded + tested 2026-05-18. Output: cache/ml_edge_predictions.json + infra/prototype/ ml_edge_predictions.json</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>ml/run_ml_edge.py post-prediction loop · schwab_client.get_quotes_batch</t>
+          <t>infra/launchd/com.swingtrade.ml-edge.plist + .ml-edge-intraday.plist (installed at ~/Library/LaunchAgents/)</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr"/>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-STRESS</t>
+          <t>AIPRED-SCHWAB</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
@@ -9314,22 +9314,22 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Stress</t>
+          <t>ML Edge / Real Quotes</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>VIX-regime stress overlay from real historical buckets</t>
+          <t>Real Schwab bid/ask spread overlay (top-100)</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>Replaces fixed heuristic shift with bucketed mean from 355K samples (base=355K, spy_down=156K, vix=37K). UI cone label shows 'STRESS · real' vs 'STRESS · heuristic' fallback</t>
+          <t>Batch-fetches live Schwab quotes for top-100 picks per mode; overrides ADV-band heuristic with real spread_bps; q50_net recomputed; spread_source='schwab_live' stamped</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>scripts/build_stress_buckets.py · cache/ml/stress_buckets.json · /api/ml-edge-stress-buckets · kairos.html _qdMlAiCone</t>
+          <t>ml/run_ml_edge.py post-prediction loop · schwab_client.get_quotes_batch</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr"/>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-SURVIVORSHIP</t>
+          <t>AIPRED-STRESS</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
@@ -9368,22 +9368,22 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Survivorship</t>
+          <t>ML Edge / Stress</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>Point-in-time R1000/R2000 membership snapshots</t>
+          <t>VIX-regime stress overlay from real historical buckets</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>Monthly launchd snapshots S&amp;P/R1000/R2000 to data/membership/*_YYYY-MM.csv. data_fetcher.get_universe_as_of reads them when present. Today's baseline captured 2026-05</t>
+          <t>Replaces fixed heuristic shift with bucketed mean from 355K samples (base=355K, spy_down=156K, vix=37K). UI cone label shows 'STRESS · real' vs 'STRESS · heuristic' fallback</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>scripts/snapshot_membership.py + infra/launchd/com.swingtrade.membership-snapshot.plist + data_fetcher.py</t>
+          <t>scripts/build_stress_buckets.py · cache/ml/stress_buckets.json · /api/ml-edge-stress-buckets · kairos.html _qdMlAiCone</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-TRACK</t>
+          <t>AIPRED-SURVIVORSHIP</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
@@ -9422,22 +9422,22 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Track Record</t>
+          <t>ML Edge / Survivorship</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>ML-Edge paper picks history + outcome resolver</t>
+          <t>Point-in-time R1000/R2000 membership snapshots</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>30 top picks per mode logged to cache/ml_edge_picks_history.jsonl on every run. scripts/resolve_ml_picks.py backfills outcomes via OHLCV lookup. /api/ml-edge-track serves real WR/PF/expectancy</t>
+          <t>Monthly launchd snapshots S&amp;P/R1000/R2000 to data/membership/*_YYYY-MM.csv. data_fetcher.get_universe_as_of reads them when present. Today's baseline captured 2026-05</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>ml/run_ml_edge.py picks-capture block + scripts/resolve_ml_picks.py + server.py /api/ml-edge-track</t>
+          <t>scripts/snapshot_membership.py + infra/launchd/com.swingtrade.membership-snapshot.plist + data_fetcher.py</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-UNIVERSE</t>
+          <t>AIPRED-TRACK</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
@@ -9476,22 +9476,22 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Universe</t>
+          <t>ML Edge / Track Record</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>Universe expansion S&amp;P 500 + R1000 + R2000 (2960 tickers)</t>
+          <t>ML-Edge paper picks history + outcome resolver</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>ml/universe_loader.py aggregates EODHD index_components for all 3 indices · --universe flag on run_ml_edge.py · membership flags stamped per-payload · S&amp;P 500=503, R1000=981, R2000=1963, union=2960</t>
+          <t>30 top picks per mode logged to cache/ml_edge_picks_history.jsonl on every run. scripts/resolve_ml_picks.py backfills outcomes via OHLCV lookup. /api/ml-edge-track serves real WR/PF/expectancy</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>ml/universe_loader.py + ml/run_ml_edge.py + UI universe pills in coverage banner</t>
+          <t>ml/run_ml_edge.py picks-capture block + scripts/resolve_ml_picks.py + server.py /api/ml-edge-track</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
@@ -9514,13 +9514,13 @@
       </c>
       <c r="N167" s="8" t="inlineStr"/>
     </row>
-    <row r="168" ht="90" customHeight="1">
+    <row r="168" ht="60" customHeight="1">
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>AIPRED-UNIVERSE</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
@@ -9530,35 +9530,27 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>ML Edge / Universe</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Universe expansion S&amp;P 500 + R1000 + R2000 (2960 tickers)</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>ml/universe_loader.py aggregates EODHD index_components for all 3 indices · --universe flag on run_ml_edge.py · membership flags stamped per-payload · S&amp;P 500=503, R1000=981, R2000=1963, union=2960</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
+          <t>ml/universe_loader.py + ml/run_ml_edge.py + UI universe pills in coverage banner</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
       <c r="I168" s="5" t="inlineStr"/>
-      <c r="J168" s="5" t="inlineStr">
-        <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
-        </is>
-      </c>
+      <c r="J168" s="5" t="inlineStr"/>
       <c r="K168" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9566,27 +9558,23 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
-        </is>
-      </c>
-      <c r="N168" s="8" t="inlineStr">
-        <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N168" s="8" t="inlineStr"/>
+    </row>
+    <row r="169" ht="90" customHeight="1">
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
@@ -9601,28 +9589,28 @@
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I169" s="5" t="inlineStr"/>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K169" s="12" t="inlineStr">
@@ -9642,17 +9630,17 @@
       </c>
       <c r="N169" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="135" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="75" customHeight="1">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
@@ -9662,37 +9650,33 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / High win</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr"/>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K170" s="12" t="inlineStr">
@@ -9707,22 +9691,22 @@
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N170" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="45" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="135" customHeight="1">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>OPS-DEPLOYMENT-RECONCILE</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
@@ -9732,27 +9716,39 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>Capture 21 untracked live launchd jobs into repo</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>deployment drift audit — 21 live jobs were running but never committed; captured into infra/launchd so repo is source of truth (55 tracked)</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/*.plist</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr"/>
-      <c r="I171" s="5" t="inlineStr"/>
-      <c r="J171" s="5" t="inlineStr"/>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / High win</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+        </is>
+      </c>
       <c r="K171" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9760,15 +9756,19 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>3138900c3</t>
-        </is>
-      </c>
-      <c r="N171" s="8" t="inlineStr"/>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+        </is>
+      </c>
+      <c r="N171" s="8" t="inlineStr">
+        <is>
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="45" customHeight="1">
       <c r="A172" s="2" t="n">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>OPS-JOB-RESTRUCTURE</t>
+          <t>OPS-DEPLOYMENT-RECONCILE</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>Launchd job restructure (lean + quota-safe)</t>
+          <t>Capture 21 untracked live launchd jobs into repo</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>daily 6x-&gt;2x, premarket/prewarm/ml-edge/schwab/optionsflow trims, 6 snapshots-&gt;1, 10 notifs-&gt;3, EODHD budget guard, ML-into-scan + cached-bar reuse</t>
+          <t>deployment drift audit — 21 live jobs were running but never committed; captured into infra/launchd so repo is source of truth (55 tracked)</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/* + eodhd_client guard + swing_trade ML hook</t>
+          <t>infra/launchd/*.plist</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>801e0d90e</t>
+          <t>3138900c3</t>
         </is>
       </c>
       <c r="N172" s="8" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>OPS-JOB-RESTRUCTURE</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
@@ -9840,39 +9840,27 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>Launchd job restructure (lean + quota-safe)</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>daily 6x-&gt;2x, premarket/prewarm/ml-edge/schwab/optionsflow trims, 6 snapshots-&gt;1, 10 notifs-&gt;3, EODHD budget guard, ML-into-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I173" s="5" t="inlineStr">
-        <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
-        </is>
-      </c>
-      <c r="J173" s="5" t="inlineStr">
-        <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
-        </is>
-      </c>
+          <t>infra/launchd/* + eodhd_client guard + swing_trade ML hook</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="5" t="inlineStr"/>
+      <c r="J173" s="5" t="inlineStr"/>
       <c r="K173" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9880,19 +9868,15 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
-        </is>
-      </c>
-      <c r="N173" s="8" t="inlineStr">
-        <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
+          <t>801e0d90e</t>
+        </is>
+      </c>
+      <c r="N173" s="8" t="inlineStr"/>
     </row>
     <row r="174" ht="45" customHeight="1">
       <c r="A174" s="2" t="n">
@@ -9900,7 +9884,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -9915,32 +9899,32 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K174" s="12" t="inlineStr">
@@ -9955,22 +9939,22 @@
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N174" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="120" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="45" customHeight="1">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -9985,32 +9969,32 @@
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J175" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K175" s="12" t="inlineStr">
@@ -10020,27 +10004,27 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N175" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="135" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="120" customHeight="1">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
@@ -10055,32 +10039,32 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K176" s="12" t="inlineStr">
@@ -10095,22 +10079,22 @@
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N176" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="75" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="135" customHeight="1">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -10120,29 +10104,37 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr"/>
-      <c r="I177" s="5" t="inlineStr"/>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+        </is>
+      </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K177" s="12" t="inlineStr">
@@ -10157,22 +10149,22 @@
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N177" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="105" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="75" customHeight="1">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
@@ -10182,37 +10174,29 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs</t>
-        </is>
-      </c>
-      <c r="I178" s="5" t="inlineStr">
-        <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="5" t="inlineStr"/>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K178" s="12" t="inlineStr">
@@ -10227,22 +10211,22 @@
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N178" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="60" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="105" customHeight="1">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -10257,32 +10241,32 @@
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
         </is>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K179" s="12" t="inlineStr">
@@ -10297,22 +10281,22 @@
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N179" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="60" customHeight="1">
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
@@ -10327,32 +10311,32 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K180" s="12" t="inlineStr">
@@ -10367,22 +10351,22 @@
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N180" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="105" customHeight="1">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -10392,37 +10376,37 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J181" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K181" s="12" t="inlineStr">
@@ -10432,27 +10416,27 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N181" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="120" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="60" customHeight="1">
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -10462,37 +10446,37 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K182" s="12" t="inlineStr">
@@ -10502,7 +10486,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
@@ -10512,17 +10496,17 @@
       </c>
       <c r="N182" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="75" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="120" customHeight="1">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
@@ -10532,37 +10516,37 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J183" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K183" s="12" t="inlineStr">
@@ -10572,27 +10556,27 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N183" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="60" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="75" customHeight="1">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
@@ -10607,17 +10591,17 @@
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -10627,12 +10611,12 @@
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K184" s="12" t="inlineStr">
@@ -10652,17 +10636,17 @@
       </c>
       <c r="N184" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="60" customHeight="1">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
@@ -10672,22 +10656,22 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10697,12 +10681,12 @@
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J185" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K185" s="12" t="inlineStr">
@@ -10717,22 +10701,22 @@
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N185" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="90" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="75" customHeight="1">
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
@@ -10742,37 +10726,37 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K186" s="12" t="inlineStr">
@@ -10782,17 +10766,17 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N186" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10786,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
@@ -10812,27 +10796,39 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="5" t="inlineStr"/>
-      <c r="J187" s="5" t="inlineStr"/>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>shipped (additive only)</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+        </is>
+      </c>
       <c r="K187" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10845,18 +10841,22 @@
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N187" s="8" t="inlineStr"/>
-    </row>
-    <row r="188" ht="45" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N187" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="90" customHeight="1">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>RISK-CB-PAPER-OFF</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C188" s="9" t="inlineStr">
@@ -10866,22 +10866,22 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Risk / Paper</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Circuit breaker fully disabled for paper trading</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>drawdown circuit breaker OFF (config disabled flag honored in portfolio_tracker), 90-day Slack review reminder via daily scan</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>config.json circuit_breaker + portfolio_tracker + swing_trade reminder</t>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
@@ -10894,23 +10894,23 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>d85c5ac2d</t>
+          <t>4442fa300</t>
         </is>
       </c>
       <c r="N188" s="8" t="inlineStr"/>
     </row>
-    <row r="189" ht="105" customHeight="1">
+    <row r="189" ht="45" customHeight="1">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>RISK-CB-PAPER-OFF</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
@@ -10920,31 +10920,27 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Risk / Paper</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Circuit breaker fully disabled for paper trading</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>drawdown circuit breaker OFF (config disabled flag honored in portfolio_tracker), 90-day Slack review reminder via daily scan</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
+          <t>config.json circuit_breaker + portfolio_tracker + swing_trade reminder</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="5" t="inlineStr"/>
-      <c r="J189" s="5" t="inlineStr">
-        <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
-        </is>
-      </c>
+      <c r="J189" s="5" t="inlineStr"/>
       <c r="K189" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10952,27 +10948,23 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
-        </is>
-      </c>
-      <c r="N189" s="8" t="inlineStr">
-        <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="90" customHeight="1">
+          <t>d85c5ac2d</t>
+        </is>
+      </c>
+      <c r="N189" s="8" t="inlineStr"/>
+    </row>
+    <row r="190" ht="105" customHeight="1">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>NEWS-DESAT-1</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C190" s="9" t="inlineStr">
@@ -10982,27 +10974,31 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Scoring</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>News sentiment saturation</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>compute_news_sentiment_score scored each insight by discrete +/-1 label and omitted neutral from denominator -&gt; 86% of universe pinned bullish, 73% pegged source_score=1.0, only 1 bearish in 908; NEWS_MOMENTUM tag fired on 86%; catalyst pillar awarded ~+1.71 pts to nearly every name (non-discriminating constant).</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>continuous_polarity flag (scoring.news_sentiment, default ON): average continuous (pos-neg) polarity from sentiment_reasoning over ALL insights, neutral=0 in denominator. Recalibrated NEWS_MOMENTUM tag + catalyst-pts thresholds to new compressed scale. Result: bullish 86-&gt;15%, pegged 73-&gt;0%, tag 86-&gt;15%. Rollback=false reproduces legacy exactly.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="5" t="inlineStr"/>
-      <c r="J190" s="5" t="inlineStr"/>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
       <c r="K190" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11010,15 +11006,19 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
-        </is>
-      </c>
-      <c r="N190" s="8" t="inlineStr"/>
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N190" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="90" customHeight="1">
       <c r="A191" s="2" t="n">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>BREAKOUT-BYPASS-LIVE</t>
+          <t>NEWS-DESAT-1</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
@@ -11036,22 +11036,22 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Signals · Gating</t>
+          <t>Scoring</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Breakout-alpha entry_quality bypass enabled</t>
+          <t>News sentiment saturation</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>Alpha setups (VCP/52wk/10WP) were demoted to WATCH by entry_quality EXTENDED/MISSED gate (their natural state) + hidden under broad families. Surfaced granular setup_type in scanner + enabled entry_quality_breakout_bypass for alpha sub-types only (TC/BE excluded). Regime score floor still applies. Paper observation; backtest cant validate verdict changes.</t>
+          <t>compute_news_sentiment_score scored each insight by discrete +/-1 label and omitted neutral from denominator -&gt; 86% of universe pinned bullish, 73% pegged source_score=1.0, only 1 bearish in 908; NEWS_MOMENTUM tag fired on 86%; catalyst pillar awarded ~+1.71 pts to nearly every name (non-discriminating constant).</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>config.entry_quality_breakout_bypass._enabled=true + analysis.make_decision bypass + server setup_type surfacing</t>
+          <t>continuous_polarity flag (scoring.news_sentiment, default ON): average continuous (pos-neg) polarity from sentiment_reasoning over ALL insights, neutral=0 in denominator. Recalibrated NEWS_MOMENTUM tag + catalyst-pts thresholds to new compressed scale. Result: bullish 86-&gt;15%, pegged 73-&gt;0%, tag 86-&gt;15%. Rollback=false reproduces legacy exactly.</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -11064,23 +11064,23 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>cc4338d9d</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N191" s="8" t="inlineStr"/>
     </row>
-    <row r="192" ht="60" customHeight="1">
+    <row r="192" ht="90" customHeight="1">
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-VERDICT-ALIGN</t>
+          <t>BREAKOUT-BYPASS-LIVE</t>
         </is>
       </c>
       <c r="C192" s="9" t="inlineStr">
@@ -11090,22 +11090,22 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Signals · Sizing</t>
+          <t>Signals · Gating</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
+          <t>Breakout-alpha entry_quality bypass enabled</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
+          <t>Alpha setups (VCP/52wk/10WP) were demoted to WATCH by entry_quality EXTENDED/MISSED gate (their natural state) + hidden under broad families. Surfaced granular setup_type in scanner + enabled entry_quality_breakout_bypass for alpha sub-types only (TC/BE excluded). Regime score floor still applies. Paper observation; backtest cant validate verdict changes.</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
+          <t>config.entry_quality_breakout_bypass._enabled=true + analysis.make_decision bypass + server setup_type surfacing</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr"/>
@@ -11123,18 +11123,18 @@
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>6a5a50549</t>
+          <t>cc4338d9d</t>
         </is>
       </c>
       <c r="N192" s="8" t="inlineStr"/>
     </row>
-    <row r="193" ht="45" customHeight="1">
+    <row r="193" ht="60" customHeight="1">
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>CONVICTION-VERDICT-ALIGN</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
@@ -11144,39 +11144,27 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Signals · Sizing</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I193" s="5" t="inlineStr">
-        <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
-        </is>
-      </c>
-      <c r="J193" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
-        </is>
-      </c>
+          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="5" t="inlineStr"/>
+      <c r="J193" s="5" t="inlineStr"/>
       <c r="K193" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11184,27 +11172,23 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
-        </is>
-      </c>
-      <c r="N193" s="8" t="inlineStr">
-        <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="90" customHeight="1">
+          <t>6a5a50549</t>
+        </is>
+      </c>
+      <c r="N193" s="8" t="inlineStr"/>
+    </row>
+    <row r="194" ht="45" customHeight="1">
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C194" s="9" t="inlineStr">
@@ -11214,37 +11198,37 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>Low / High (transparency + future-proof)</t>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
         </is>
       </c>
       <c r="J194" s="5" t="inlineStr">
         <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K194" s="12" t="inlineStr">
@@ -11259,22 +11243,22 @@
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N194" s="8" t="inlineStr">
         <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="75" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="90" customHeight="1">
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M21-INFRA</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
@@ -11284,27 +11268,39 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr"/>
-      <c r="I195" s="5" t="inlineStr"/>
-      <c r="J195" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>Low / High (transparency + future-proof)</t>
+        </is>
+      </c>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
       <c r="K195" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11312,7 +11308,7 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
@@ -11320,15 +11316,19 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="N195" s="8" t="inlineStr"/>
-    </row>
-    <row r="196" ht="90" customHeight="1">
+      <c r="N195" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="75" customHeight="1">
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M22-DATA</t>
+          <t>STRUCT-TARGETS-M21-INFRA</t>
         </is>
       </c>
       <c r="C196" s="9" t="inlineStr">
@@ -11343,17 +11343,17 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
+          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
+          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
+          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M23-MODES</t>
+          <t>STRUCT-TARGETS-M22-DATA</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
@@ -11397,17 +11397,17 @@
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
+          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
+          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
+          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -11430,13 +11430,13 @@
       </c>
       <c r="N197" s="8" t="inlineStr"/>
     </row>
-    <row r="198" ht="75" customHeight="1">
+    <row r="198" ht="90" customHeight="1">
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+          <t>STRUCT-TARGETS-M23-MODES</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
@@ -11451,17 +11451,17 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.4 — regression suite + monitoring</t>
+          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
+          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
+          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>STRUCT-TARGETS-M24-VALIDATION</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
@@ -11500,22 +11500,22 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Structural targets · M2.4 — regression suite + monitoring</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
@@ -11528,23 +11528,23 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N199" s="8" t="inlineStr"/>
     </row>
-    <row r="200" ht="60" customHeight="1">
+    <row r="200" ht="75" customHeight="1">
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
@@ -11554,39 +11554,27 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
-        </is>
-      </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I200" s="5" t="inlineStr">
-        <is>
-          <t>Win: continuous drift visibility between alert events.</t>
-        </is>
-      </c>
-      <c r="J200" s="5" t="inlineStr">
-        <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="5" t="inlineStr"/>
+      <c r="J200" s="5" t="inlineStr"/>
       <c r="K200" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11594,27 +11582,23 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-      <c r="N200" s="8" t="inlineStr">
-        <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N200" s="8" t="inlineStr"/>
+    </row>
+    <row r="201" ht="60" customHeight="1">
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
@@ -11624,37 +11608,37 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J201" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K201" s="12" t="inlineStr">
@@ -11669,22 +11653,22 @@
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N201" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="105" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="45" customHeight="1">
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C202" s="9" t="inlineStr">
@@ -11699,24 +11683,32 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr"/>
-      <c r="I202" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
       <c r="J202" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K202" s="12" t="inlineStr">
@@ -11726,17 +11718,17 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N202" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11738,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
@@ -11761,24 +11753,24 @@
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
       <c r="I203" s="5" t="inlineStr"/>
       <c r="J203" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K203" s="12" t="inlineStr">
@@ -11793,22 +11785,22 @@
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N203" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="105" customHeight="1">
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C204" s="9" t="inlineStr">
@@ -11818,37 +11810,29 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
-        </is>
-      </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I204" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="5" t="inlineStr"/>
       <c r="J204" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K204" s="12" t="inlineStr">
@@ -11863,12 +11847,12 @@
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N204" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11862,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
@@ -11888,35 +11872,39 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J205" s="5" t="inlineStr"/>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J205" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K205" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11929,22 +11917,22 @@
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N205" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="105" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="45" customHeight="1">
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C206" s="9" t="inlineStr">
@@ -11954,39 +11942,35 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J206" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J206" s="5" t="inlineStr"/>
       <c r="K206" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11999,22 +11983,22 @@
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N206" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="45" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="105" customHeight="1">
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSE-NASDAQ-1000</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
@@ -12024,27 +12008,39 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Universe</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>NASDAQ 1000 liquidity gate</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="inlineStr"/>
-      <c r="I207" s="5" t="inlineStr"/>
-      <c r="J207" s="5" t="inlineStr"/>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>1.5 hrs</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K207" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12052,15 +12048,19 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>ab1deacef</t>
-        </is>
-      </c>
-      <c r="N207" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N207" s="8" t="inlineStr">
+        <is>
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="45" customHeight="1">
       <c r="A208" s="2" t="n">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-KAIROS-DOSSIER</t>
+          <t>UNIVERSE-NASDAQ-1000</t>
         </is>
       </c>
       <c r="C208" s="9" t="inlineStr">
@@ -12078,22 +12078,22 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Kairos</t>
+          <t>Universe</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
+          <t>NASDAQ 1000 liquidity gate</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
+          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html kaiTickerDossier</t>
+          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>e3baa715f</t>
+          <t>ab1deacef</t>
         </is>
       </c>
       <c r="N208" s="8" t="inlineStr"/>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>REGIME-ACCURACY-TEST</t>
+          <t>STOCKSMITH-KAIROS-DOSSIER</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
@@ -12132,22 +12132,22 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Validation / Regime</t>
+          <t>V2 Dashboard / Kairos</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Regime-classification accuracy test (principle 18)</t>
+          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
+          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>scripts/regime_accuracy.py</t>
+          <t>Stocksmith.html kaiTickerDossier</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
@@ -12160,48 +12160,48 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
+          <t>e3baa715f</t>
         </is>
       </c>
       <c r="N209" s="8" t="inlineStr"/>
     </row>
-    <row r="210" ht="90" customHeight="1">
+    <row r="210" ht="45" customHeight="1">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>MORNING-BRIEF-STALE</t>
-        </is>
-      </c>
-      <c r="C210" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>REGIME-ACCURACY-TEST</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>Validation / Regime</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Morning briefing exit=2 (stale tickers.json)</t>
+          <t>Regime-classification accuracy test (principle 18)</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>morning_briefing.py aborts (exit 2) when infra/prototype/tickers.json &gt;24h old. Root cause: build_data.py (writes tickers.json at scan end) intermittently exceeds the 180s subprocess timeout in swing_trade.py on cold caches -&gt; tickers.json not refreshed -&gt; stale -&gt; briefing aborts. Compounded by transient Slack DNS failures when the Mac is asleep at 6:30am</t>
+          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>Raised build_data.py subprocess timeout 180-&gt;360s in swing_trade.py (2x headroom). Manually refreshed tickers.json. Residual: machine must be awake/online at 6:30 PT for briefing+all alerts to post</t>
+          <t>scripts/regime_accuracy.py</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
@@ -12214,12 +12214,12 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>e7721f05c</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N210" s="8" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>SIGNAL-ALERTS-1</t>
+          <t>MORNING-BRIEF-STALE</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -12245,17 +12245,17 @@
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Daily WATCH-to-BUY flip + new Elite Pick alerts</t>
+          <t>Morning briefing exit=2 (stale tickers.json)</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Owner wanted Slack alerts for (a) firm BUY-candidate from entry-watcher, (b) names flipping to BUY day-over-day, (c) new Elite Picks per mode</t>
+          <t>morning_briefing.py aborts (exit 2) when infra/prototype/tickers.json &gt;24h old. Root cause: build_data.py (writes tickers.json at scan end) intermittently exceeds the 180s subprocess timeout in swing_trade.py on cold caches -&gt; tickers.json not refreshed -&gt; stale -&gt; briefing aborts. Compounded by transient Slack DNS failures when the Mac is asleep at 6:30am</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>entry_watch.py: distinct shadow BUY-CANDIDATE message (#a). signal_alerts.py: day-over-day diff of per-mode BUY lists (buy_candidates/medium_term_picks/long_term_picks) + elite_picks vs data/signal_alert_snapshot.json; grouped digest; LIVE to owner Slack with composite-score caveat; launchd com.swingtrade.signal-alerts 7:15 PT daily. Zero EODHD</t>
+          <t>Raised build_data.py subprocess timeout 180-&gt;360s in swing_trade.py (2x headroom). Manually refreshed tickers.json. Residual: machine must be awake/online at 6:30 PT for briefing+all alerts to post</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
@@ -12273,18 +12273,18 @@
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>116e27f63</t>
+          <t>e7721f05c</t>
         </is>
       </c>
       <c r="N211" s="8" t="inlineStr"/>
     </row>
-    <row r="212" ht="75" customHeight="1">
+    <row r="212" ht="90" customHeight="1">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>SLEEVE-ALERTS</t>
+          <t>SIGNAL-ALERTS-1</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12299,17 +12299,17 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Dedicated catalyst-sleeve signal alerts</t>
+          <t>Daily WATCH-to-BUY flip + new Elite Pick alerts</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Entry-watcher covers price-action setups (pullback/breakout/impulse) but the 7 catalyst sleeves (PEAD/Insider/ESP/MeanRev/Momentum/DefRot) had no dedicated alert — they only reached Slack indirectly via flip/elite digests. Per principle 14 these are the higher-mechanism signals (PEAD PF 2.04, Momentum 1.53)</t>
+          <t>Owner wanted Slack alerts for (a) firm BUY-candidate from entry-watcher, (b) names flipping to BUY day-over-day, (c) new Elite Picks per mode</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>signal_alerts.py: added SLEEVES dimension; _current_state tracks &lt;field&gt;.fired per sleeve; daily diff emits '🧬 New catalyst signal(s)' clean card on new entrants; Phase-1 paper-validation note. Fire rarely (0 today) so low-noise/high-value. Snapshot re-seeded with sleeves key</t>
+          <t>entry_watch.py: distinct shadow BUY-CANDIDATE message (#a). signal_alerts.py: day-over-day diff of per-mode BUY lists (buy_candidates/medium_term_picks/long_term_picks) + elite_picks vs data/signal_alert_snapshot.json; grouped digest; LIVE to owner Slack with composite-score caveat; launchd com.swingtrade.signal-alerts 7:15 PT daily. Zero EODHD</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
@@ -12327,18 +12327,18 @@
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>fa8835903</t>
+          <t>116e27f63</t>
         </is>
       </c>
       <c r="N212" s="8" t="inlineStr"/>
     </row>
-    <row r="213" ht="90" customHeight="1">
+    <row r="213" ht="75" customHeight="1">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
+          <t>SLEEVE-ALERTS</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12348,22 +12348,22 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Dedicated catalyst-sleeve signal alerts</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>Entry-watcher covers price-action setups (pullback/breakout/impulse) but the 7 catalyst sleeves (PEAD/Insider/ESP/MeanRev/Momentum/DefRot) had no dedicated alert — they only reached Slack indirectly via flip/elite digests. Per principle 14 these are the higher-mechanism signals (PEAD PF 2.04, Momentum 1.53)</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>signal_alerts.py: added SLEEVES dimension; _current_state tracks &lt;field&gt;.fired per sleeve; daily diff emits '🧬 New catalyst signal(s)' clean card on new entrants; Phase-1 paper-validation note. Fire rarely (0 today) so low-noise/high-value. Snapshot re-seeded with sleeves key</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr"/>
@@ -12376,23 +12376,23 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>fa8835903</t>
         </is>
       </c>
       <c r="N213" s="8" t="inlineStr"/>
     </row>
-    <row r="214" ht="75" customHeight="1">
+    <row r="214" ht="90" customHeight="1">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>WEEKEND-PHANTOMS</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12402,22 +12402,22 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr"/>
@@ -12435,18 +12435,18 @@
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N214" s="8" t="inlineStr"/>
     </row>
-    <row r="215" ht="105" customHeight="1">
+    <row r="215" ht="75" customHeight="1">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>BULLALGO-1</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12456,22 +12456,22 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>BullVeda</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>BullAlgo — transparent LuxAlgo-style overlays + MCDX + Price Action</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Ownable, inspectable reproduction of LuxAlgo Signals&amp;Overlays + Price Action Concepts + MCDX, replacing the TradingView black box; every layer is a standard auditable indicator</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>bullalgo.py engines (Confirmation/Signals-Overlays screener/PAC screener/chart-series/PAC-chart/MCDX); server.py 4 endpoints /api/bullalgo/*; pattern_data SWING_1H mode; isolated test benches bullalgo-test.html + setup-tv-lab.html; PRODUCTION Overview integration in lens-overview.jsx (OverviewMcdx synced strip + interactive/expand setup chart + Setup&lt;-&gt;PriceAction toggle). Display-only, real data, NOT identical to LuxAlgo (transparent approximation)</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12484,23 +12484,23 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>296777349</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N215" s="8" t="inlineStr"/>
     </row>
-    <row r="216" ht="75" customHeight="1">
+    <row r="216" ht="105" customHeight="1">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>BULLALGO-FOOTPRINT</t>
+          <t>BULLALGO-1</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12510,22 +12510,22 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>BullVeda Lenses</t>
+          <t>BullVeda</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Real institutional footprint strip</t>
+          <t>BullAlgo — transparent LuxAlgo-style overlays + MCDX + Price Action</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>MCDX is interpretive momentum math (no order flow); users asked why we cant show real smart-money detail</t>
+          <t>Ownable, inspectable reproduction of LuxAlgo Signals&amp;Overlays + Price Action Concepts + MCDX, replacing the TradingView black box; every layer is a standard auditable indicator</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Added /api/bullalgo/{t}/footprint + bullalgo.footprint() aggregating REAL attributable signals: OBV/AD accumulation (live), insider Form 4 net (SEC, value-filtered), 13F institutional holders + QoQ change (EODHD). Rendered as honest counterpart strip under MCDX. No new data license.</t>
+          <t>bullalgo.py engines (Confirmation/Signals-Overlays screener/PAC screener/chart-series/PAC-chart/MCDX); server.py 4 endpoints /api/bullalgo/*; pattern_data SWING_1H mode; isolated test benches bullalgo-test.html + setup-tv-lab.html; PRODUCTION Overview integration in lens-overview.jsx (OverviewMcdx synced strip + interactive/expand setup chart + Setup&lt;-&gt;PriceAction toggle). Display-only, real data, NOT identical to LuxAlgo (transparent approximation)</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12543,18 +12543,18 @@
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>b3314aaf2</t>
+          <t>296777349</t>
         </is>
       </c>
       <c r="N216" s="8" t="inlineStr"/>
     </row>
-    <row r="217" ht="60" customHeight="1">
+    <row r="217" ht="75" customHeight="1">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>BULLALGO-LENS</t>
+          <t>BULLALGO-FOOTPRINT</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12569,17 +12569,17 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>BullAlgo native lens + MCDX alignment</t>
+          <t>Real institutional footprint strip</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Ported bullalgo-test.html prototype into a native per-ticker lens (16th, in-house LuxAlgo replacement for removed tv lens); MCDX money-flow misaligned with price chart</t>
+          <t>MCDX is interpretive momentum math (no order flow); users asked why we cant show real smart-money detail</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>lens-bullalgo.jsx + lens-bullalgo.css scoped; registered in LENSES/detail-panel/dev-loader/CapStudio; backend mcdx_series emits whitespace warmup points so bar counts match (180==180) + minimumWidth:64 on both price scales</t>
+          <t>Added /api/bullalgo/{t}/footprint + bullalgo.footprint() aggregating REAL attributable signals: OBV/AD accumulation (live), insider Form 4 net (SEC, value-filtered), 13F institutional holders + QoQ change (EODHD). Rendered as honest counterpart strip under MCDX. No new data license.</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>BULLALGO-LENS</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12618,22 +12618,22 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>BullVeda Lenses</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>BullAlgo native lens + MCDX alignment</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>Ported bullalgo-test.html prototype into a native per-ticker lens (16th, in-house LuxAlgo replacement for removed tv lens); MCDX money-flow misaligned with price chart</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>lens-bullalgo.jsx + lens-bullalgo.css scoped; registered in LENSES/detail-panel/dev-loader/CapStudio; backend mcdx_series emits whitespace warmup points so bar counts match (180==180) + minimumWidth:64 on both price scales</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12646,23 +12646,23 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>b3314aaf2</t>
         </is>
       </c>
       <c r="N218" s="8" t="inlineStr"/>
     </row>
-    <row r="219" ht="45" customHeight="1">
+    <row r="219" ht="60" customHeight="1">
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12672,22 +12672,22 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12726,22 +12726,22 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -12754,12 +12754,12 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N220" s="8" t="inlineStr"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13109,17 +13109,17 @@
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N227" s="8" t="inlineStr"/>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13752,22 +13752,22 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -13780,23 +13780,23 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N239" s="8" t="inlineStr"/>
     </row>
-    <row r="240" ht="105" customHeight="1">
+    <row r="240" ht="45" customHeight="1">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -13806,22 +13806,22 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
@@ -13839,18 +13839,18 @@
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N240" s="8" t="inlineStr"/>
     </row>
-    <row r="241" ht="75" customHeight="1">
+    <row r="241" ht="105" customHeight="1">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-T1CAT-1</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -13860,22 +13860,22 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>T1 CATALYST pill read wrong field</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr"/>
@@ -13888,12 +13888,12 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N241" s="8" t="inlineStr"/>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>SCANNER-T1CAT-1</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -13914,22 +13914,22 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>T1 CATALYST pill read wrong field</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>The scanner '⚡ T1 CATALYST' pill filtered t.tier===T1 (conviction_tier), not the catalyst tier. conviction_tier has 0 T1s on a no-BUY day (CPI blackout: AVOID 928/WATCH 133/T3 14), so the pill matched nothing — while catalyst_tier T1 = 239 names.</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>Changed the pill filter to t.cat===T1 (catalyst tier, matching the displayed CAT column). Rebuilt.</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr"/>
@@ -13942,12 +13942,12 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>1d6fdb14a</t>
         </is>
       </c>
       <c r="N242" s="8" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -13968,22 +13968,22 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr"/>
@@ -13996,23 +13996,23 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>613f10e35</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N243" s="8" t="inlineStr"/>
     </row>
-    <row r="244" ht="60" customHeight="1">
+    <row r="244" ht="75" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14022,22 +14022,22 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr"/>
@@ -14050,12 +14050,12 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>613f10e35</t>
         </is>
       </c>
       <c r="N244" s="8" t="inlineStr"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14076,34 +14076,26 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H245" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr"/>
+      <c r="I245" s="5" t="inlineStr"/>
       <c r="J245" s="5" t="inlineStr"/>
       <c r="K245" s="12" t="inlineStr">
         <is>
@@ -14112,27 +14104,23 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N245" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N245" s="8" t="inlineStr"/>
+    </row>
+    <row r="246" ht="60" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14147,17 +14135,17 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -14167,14 +14155,10 @@
       </c>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J246" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J246" s="5" t="inlineStr"/>
       <c r="K246" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14187,12 +14171,12 @@
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N246" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14186,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14217,22 +14201,34 @@
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="inlineStr"/>
-      <c r="I247" s="5" t="inlineStr"/>
-      <c r="J247" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I247" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J247" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K247" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14240,23 +14236,27 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N247" s="8" t="inlineStr"/>
-    </row>
-    <row r="248" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N247" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="75" customHeight="1">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14266,22 +14266,22 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr"/>
@@ -14294,23 +14294,23 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N248" s="8" t="inlineStr"/>
     </row>
-    <row r="249" ht="45" customHeight="1">
+    <row r="249" ht="60" customHeight="1">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14320,34 +14320,26 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I249" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr"/>
+      <c r="I249" s="5" t="inlineStr"/>
       <c r="J249" s="5" t="inlineStr"/>
       <c r="K249" s="12" t="inlineStr">
         <is>
@@ -14356,27 +14348,23 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N249" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="90" customHeight="1">
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N249" s="8" t="inlineStr"/>
+    </row>
+    <row r="250" ht="45" customHeight="1">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14386,26 +14374,34 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
-        </is>
-      </c>
-      <c r="H250" s="2" t="inlineStr"/>
-      <c r="I250" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I250" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J250" s="5" t="inlineStr"/>
       <c r="K250" s="12" t="inlineStr">
         <is>
@@ -14414,23 +14410,27 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N250" s="8" t="inlineStr"/>
-    </row>
-    <row r="251" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N250" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="90" customHeight="1">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14440,39 +14440,27 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I251" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J251" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr"/>
+      <c r="I251" s="5" t="inlineStr"/>
+      <c r="J251" s="5" t="inlineStr"/>
       <c r="K251" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14480,19 +14468,15 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N251" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N251" s="8" t="inlineStr"/>
     </row>
     <row r="252" ht="45" customHeight="1">
       <c r="A252" s="2" t="n">
@@ -14500,7 +14484,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14510,27 +14494,39 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H252" s="2" t="inlineStr"/>
-      <c r="I252" s="5" t="inlineStr"/>
-      <c r="J252" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I252" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J252" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K252" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14538,15 +14534,19 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N252" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N252" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="45" customHeight="1">
       <c r="A253" s="2" t="n">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14564,22 +14564,22 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr"/>
@@ -14597,18 +14597,18 @@
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N253" s="8" t="inlineStr"/>
     </row>
-    <row r="254" ht="75" customHeight="1">
+    <row r="254" ht="45" customHeight="1">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14618,39 +14618,27 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I254" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J254" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr"/>
+      <c r="I254" s="5" t="inlineStr"/>
+      <c r="J254" s="5" t="inlineStr"/>
       <c r="K254" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14658,27 +14646,23 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N254" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N254" s="8" t="inlineStr"/>
+    </row>
+    <row r="255" ht="75" customHeight="1">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14688,37 +14672,37 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J255" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K255" s="12" t="inlineStr">
@@ -14728,17 +14712,17 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N255" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14732,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
@@ -14763,32 +14747,32 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J256" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K256" s="12" t="inlineStr">
@@ -14808,7 +14792,7 @@
       </c>
       <c r="N256" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -14818,7 +14802,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
@@ -14833,32 +14817,32 @@
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J257" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K257" s="12" t="inlineStr">
@@ -14878,7 +14862,7 @@
       </c>
       <c r="N257" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14872,7 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
@@ -14903,32 +14887,32 @@
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J258" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K258" s="12" t="inlineStr">
@@ -14938,27 +14922,27 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N258" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="60" customHeight="1">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -14968,27 +14952,39 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H259" s="2" t="inlineStr"/>
-      <c r="I259" s="5" t="inlineStr"/>
-      <c r="J259" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I259" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J259" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K259" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14996,15 +14992,19 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N259" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N259" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="45" customHeight="1">
       <c r="A260" s="2" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
@@ -15060,13 +15060,13 @@
       </c>
       <c r="N260" s="8" t="inlineStr"/>
     </row>
-    <row r="261" ht="60" customHeight="1">
+    <row r="261" ht="45" customHeight="1">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -15076,22 +15076,22 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -15104,23 +15104,23 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N261" s="8" t="inlineStr"/>
     </row>
-    <row r="262" ht="150" customHeight="1">
+    <row r="262" ht="60" customHeight="1">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
@@ -15130,31 +15130,27 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
       <c r="I262" s="5" t="inlineStr"/>
-      <c r="J262" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J262" s="5" t="inlineStr"/>
       <c r="K262" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15162,27 +15158,23 @@
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N262" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="105" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N262" s="8" t="inlineStr"/>
+    </row>
+    <row r="263" ht="150" customHeight="1">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
@@ -15192,27 +15184,31 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
       <c r="I263" s="5" t="inlineStr"/>
-      <c r="J263" s="5" t="inlineStr"/>
+      <c r="J263" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K263" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15220,23 +15216,27 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
-        </is>
-      </c>
-      <c r="N263" s="8" t="inlineStr"/>
-    </row>
-    <row r="264" ht="45" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N263" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="105" customHeight="1">
       <c r="A264" s="2" t="n">
         <v>263</v>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15246,22 +15246,22 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -15274,12 +15274,12 @@
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N264" s="8" t="inlineStr"/>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15305,17 +15305,17 @@
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15467,17 +15467,17 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15521,17 +15521,17 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15575,17 +15575,17 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15683,17 +15683,17 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15737,17 +15737,17 @@
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15791,17 +15791,17 @@
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15845,17 +15845,17 @@
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -15878,13 +15878,13 @@
       </c>
       <c r="N275" s="8" t="inlineStr"/>
     </row>
-    <row r="276" ht="60" customHeight="1">
+    <row r="276" ht="45" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15894,22 +15894,22 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -15922,23 +15922,23 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N276" s="8" t="inlineStr"/>
     </row>
-    <row r="277" ht="120" customHeight="1">
+    <row r="277" ht="60" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15948,39 +15948,27 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H277" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I277" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J277" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr"/>
+      <c r="I277" s="5" t="inlineStr"/>
+      <c r="J277" s="5" t="inlineStr"/>
       <c r="K277" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15988,27 +15976,23 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N277" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="75" customHeight="1">
+          <t>cf702f2b4</t>
+        </is>
+      </c>
+      <c r="N277" s="8" t="inlineStr"/>
+    </row>
+    <row r="278" ht="120" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -16018,27 +16002,39 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H278" s="2" t="inlineStr"/>
-      <c r="I278" s="5" t="inlineStr"/>
-      <c r="J278" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I278" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J278" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K278" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16046,23 +16042,27 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N278" s="8" t="inlineStr"/>
-    </row>
-    <row r="279" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N278" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="75" customHeight="1">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -16072,22 +16072,22 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -16100,23 +16100,23 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N279" s="8" t="inlineStr"/>
     </row>
-    <row r="280" ht="45" customHeight="1">
+    <row r="280" ht="60" customHeight="1">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16131,17 +16131,17 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -16164,13 +16164,13 @@
       </c>
       <c r="N280" s="8" t="inlineStr"/>
     </row>
-    <row r="281" ht="60" customHeight="1">
+    <row r="281" ht="45" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16185,17 +16185,17 @@
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
@@ -16218,13 +16218,13 @@
       </c>
       <c r="N281" s="8" t="inlineStr"/>
     </row>
-    <row r="282" ht="45" customHeight="1">
+    <row r="282" ht="60" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16239,17 +16239,17 @@
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
@@ -16267,7 +16267,7 @@
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N282" s="8" t="inlineStr"/>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16293,17 +16293,17 @@
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr"/>
@@ -16326,13 +16326,13 @@
       </c>
       <c r="N283" s="8" t="inlineStr"/>
     </row>
-    <row r="284" ht="120" customHeight="1">
+    <row r="284" ht="45" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16342,22 +16342,22 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
@@ -16370,23 +16370,23 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N284" s="8" t="inlineStr"/>
     </row>
-    <row r="285" ht="60" customHeight="1">
+    <row r="285" ht="120" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>TE-SESSION-CACHE</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16396,22 +16396,22 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Structural Targets</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>Session-date cache invalidation</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr"/>
@@ -16424,12 +16424,12 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>33146be5e</t>
+          <t>93ec11842</t>
         </is>
       </c>
       <c r="N285" s="8" t="inlineStr"/>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>TE-SESSION-CACHE</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Structural Targets</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>Session-date cache invalidation</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr"/>
@@ -16478,23 +16478,23 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>33146be5e</t>
         </is>
       </c>
       <c r="N286" s="8" t="inlineStr"/>
     </row>
-    <row r="287" ht="105" customHeight="1">
+    <row r="287" ht="60" customHeight="1">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C287" s="10" t="inlineStr">
@@ -16504,31 +16504,27 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr"/>
       <c r="I287" s="5" t="inlineStr"/>
-      <c r="J287" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J287" s="5" t="inlineStr"/>
       <c r="K287" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16536,27 +16532,23 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N287" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="135" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N287" s="8" t="inlineStr"/>
+    </row>
+    <row r="288" ht="105" customHeight="1">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C288" s="10" t="inlineStr">
@@ -16566,37 +16558,29 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H288" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I288" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="5" t="inlineStr"/>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K288" s="12" t="inlineStr">
@@ -16606,27 +16590,27 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N288" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="135" customHeight="1">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C289" s="10" t="inlineStr">
@@ -16636,27 +16620,39 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H289" s="2" t="inlineStr"/>
-      <c r="I289" s="5" t="inlineStr"/>
-      <c r="J289" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I289" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J289" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K289" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16664,23 +16660,27 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N289" s="8" t="inlineStr"/>
-    </row>
-    <row r="290" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N289" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="45" customHeight="1">
       <c r="A290" s="2" t="n">
         <v>289</v>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C290" s="10" t="inlineStr">
@@ -16690,31 +16690,27 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr"/>
       <c r="I290" s="5" t="inlineStr"/>
-      <c r="J290" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J290" s="5" t="inlineStr"/>
       <c r="K290" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16722,27 +16718,23 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N290" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N290" s="8" t="inlineStr"/>
+    </row>
+    <row r="291" ht="120" customHeight="1">
       <c r="A291" s="2" t="n">
         <v>290</v>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C291" s="10" t="inlineStr">
@@ -16752,27 +16744,31 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr"/>
       <c r="I291" s="5" t="inlineStr"/>
-      <c r="J291" s="5" t="inlineStr"/>
+      <c r="J291" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K291" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16780,15 +16776,19 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N291" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N291" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="60" customHeight="1">
       <c r="A292" s="2" t="n">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C292" s="10" t="inlineStr">
@@ -16806,22 +16806,22 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr"/>
@@ -16839,60 +16839,48 @@
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N292" s="8" t="inlineStr"/>
     </row>
-    <row r="293" ht="45" customHeight="1">
+    <row r="293" ht="60" customHeight="1">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C293" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C293" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H293" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I293" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J293" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr"/>
+      <c r="I293" s="5" t="inlineStr"/>
+      <c r="J293" s="5" t="inlineStr"/>
       <c r="K293" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16900,15 +16888,15 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M293" s="3" t="inlineStr"/>
-      <c r="N293" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N293" s="8" t="inlineStr"/>
     </row>
     <row r="294" ht="45" customHeight="1">
       <c r="A294" s="2" t="n">
@@ -16916,7 +16904,7 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -16931,32 +16919,32 @@
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K294" s="12" t="inlineStr">
@@ -16972,7 +16960,7 @@
       <c r="M294" s="3" t="inlineStr"/>
       <c r="N294" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -16982,7 +16970,7 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -16992,35 +16980,39 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J295" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J295" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K295" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17028,17 +17020,13 @@
       </c>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M295" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr"/>
       <c r="N295" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -17048,59 +17036,63 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C296" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C296" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J296" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K296" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L296" s="2" t="inlineStr"/>
-      <c r="M296" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J296" s="5" t="inlineStr"/>
+      <c r="K296" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N296" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17102,7 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C297" s="10" t="inlineStr">
@@ -17120,37 +17112,37 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J297" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K297" s="14" t="inlineStr">
@@ -17172,109 +17164,109 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C298" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C298" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I298" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J298" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K298" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K298" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L298" s="2" t="inlineStr"/>
       <c r="M298" s="3" t="inlineStr"/>
       <c r="N298" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="45" customHeight="1">
       <c r="A299" s="2" t="n">
         <v>298</v>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C299" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E299" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I299" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J299" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K299" s="15" t="inlineStr">
@@ -17282,147 +17274,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L299" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="3" t="inlineStr"/>
       <c r="N299" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="75" customHeight="1">
       <c r="A300" s="2" t="n">
         <v>299</v>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C300" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E300" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F300" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G300" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I300" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J300" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K300" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M300" s="3" t="inlineStr"/>
+      <c r="N300" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="195" customHeight="1">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C300" s="10" t="inlineStr">
+      <c r="C301" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D300" s="5" t="inlineStr">
+      <c r="D301" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E301" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F300" s="5" t="inlineStr">
+      <c r="F301" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G300" s="5" t="inlineStr">
+      <c r="G301" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H300" s="2" t="inlineStr">
+      <c r="H301" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I300" s="5" t="inlineStr">
+      <c r="I301" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J300" s="5" t="inlineStr">
+      <c r="J301" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K300" s="15" t="inlineStr">
+      <c r="K301" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L300" s="2" t="inlineStr">
+      <c r="L301" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M300" s="3" t="inlineStr"/>
-      <c r="N300" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="301" ht="90" customHeight="1">
-      <c r="A301" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="B301" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C301" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D301" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E301" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F301" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G301" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H301" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I301" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J301" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K301" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L301" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M301" s="3" t="inlineStr"/>
       <c r="N301" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="90" customHeight="1">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C302" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E302" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F302" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G302" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I302" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J302" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K302" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M302" s="3" t="inlineStr"/>
+      <c r="N302" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -17524,13 +17578,13 @@
         <v>32</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>83</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5">
@@ -17581,13 +17635,13 @@
         <v>35</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>150</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
